--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B32FDA8-842B-49AB-B6F8-89E30A121329}"/>
   <bookViews>
-    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1380,6 +1380,39 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1674,39 +1707,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
@@ -1716,6 +1716,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1732,15 +1743,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B32FDA8-842B-49AB-B6F8-89E30A121329}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE512990-8AE2-45FE-8871-9437531D8117}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -509,10 +509,10 @@
         <v>46204</v>
       </c>
       <c r="B8">
-        <v>78.540999999999997</v>
+        <v>79.22</v>
       </c>
       <c r="C8">
-        <v>3.0176666600000002</v>
+        <v>2.9386999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -520,10 +520,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>78.563000000000002</v>
+        <v>81.341999999999999</v>
       </c>
       <c r="C9">
-        <v>2.7669999999999999</v>
+        <v>2.8528500000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -531,10 +531,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>76.644000000000005</v>
+        <v>81.480999999999995</v>
       </c>
       <c r="C10">
-        <v>2.7879999999999998</v>
+        <v>2.7669999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -542,10 +542,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>74.792000000000002</v>
+        <v>79.680999999999997</v>
       </c>
       <c r="C11">
-        <v>2.823</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>73.572999999999993</v>
+        <v>78.212999999999994</v>
       </c>
       <c r="C12">
-        <v>3.0369999999999999</v>
+        <v>3.0760000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,10 +564,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>72.459999999999994</v>
+        <v>76.718999999999994</v>
       </c>
       <c r="C13">
-        <v>3.7519999999999998</v>
+        <v>3.677</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +575,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>71.602000000000004</v>
+        <v>75.512</v>
       </c>
       <c r="C14">
-        <v>4.2080000000000002</v>
+        <v>4.1029999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +586,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>71.036000000000001</v>
+        <v>74.709000000000003</v>
       </c>
       <c r="C15">
-        <v>3.8250000000000002</v>
+        <v>3.7440000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>70.438999999999993</v>
+        <v>73.894999999999996</v>
       </c>
       <c r="C16">
-        <v>3.0030000000000001</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,10 +608,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>69.933999999999997</v>
+        <v>73.225999999999999</v>
       </c>
       <c r="C17">
-        <v>2.85</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -619,10 +619,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>69.546000000000006</v>
+        <v>72.716999999999999</v>
       </c>
       <c r="C18">
-        <v>2.847</v>
+        <v>2.8479999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>69.186000000000007</v>
+        <v>72.225999999999999</v>
       </c>
       <c r="C19">
-        <v>2.9809999999999999</v>
+        <v>2.9820000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +641,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>68.84</v>
+        <v>71.733999999999995</v>
       </c>
       <c r="C20">
-        <v>3.1869999999999998</v>
+        <v>3.1829999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>68.576999999999998</v>
+        <v>71.358999999999995</v>
       </c>
       <c r="C21">
-        <v>3.254</v>
+        <v>3.2450000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -663,10 +663,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>68.326999999999998</v>
+        <v>70.992999999999995</v>
       </c>
       <c r="C22">
-        <v>3.23</v>
+        <v>3.2240000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,10 +674,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>68.113</v>
+        <v>70.677000000000007</v>
       </c>
       <c r="C23">
-        <v>3.306</v>
+        <v>3.2949999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,10 +685,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>67.92</v>
+        <v>70.381</v>
       </c>
       <c r="C24">
-        <v>3.55</v>
+        <v>3.5409999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,10 +696,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>67.697000000000003</v>
+        <v>70.051000000000002</v>
       </c>
       <c r="C25">
-        <v>4.2060000000000004</v>
+        <v>4.1950000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>67.507000000000005</v>
+        <v>69.762</v>
       </c>
       <c r="C26">
-        <v>4.6459999999999999</v>
+        <v>4.6470000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +718,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>67.349999999999994</v>
+        <v>69.515000000000001</v>
       </c>
       <c r="C27">
-        <v>4.2009999999999996</v>
+        <v>4.2160000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +729,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>67.180999999999997</v>
+        <v>69.242999999999995</v>
       </c>
       <c r="C28">
-        <v>3.4159999999999999</v>
+        <v>3.4260000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +740,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>67.046000000000006</v>
+        <v>69.031000000000006</v>
       </c>
       <c r="C29">
-        <v>3.1480000000000001</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>66.906000000000006</v>
+        <v>68.814999999999998</v>
       </c>
       <c r="C30">
-        <v>3.1259999999999999</v>
+        <v>3.1469999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +762,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>66.733000000000004</v>
+        <v>68.552000000000007</v>
       </c>
       <c r="C31">
-        <v>3.2570000000000001</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,10 +773,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>66.597999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="C32">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,10 +784,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>66.486999999999995</v>
+        <v>68.155000000000001</v>
       </c>
       <c r="C33">
-        <v>3.5419999999999998</v>
+        <v>3.5430000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>66.379000000000005</v>
+        <v>67.971000000000004</v>
       </c>
       <c r="C34">
-        <v>3.5190000000000001</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +806,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>66.290999999999997</v>
+        <v>67.808999999999997</v>
       </c>
       <c r="C35">
-        <v>3.5760000000000001</v>
+        <v>3.5779999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,10 +817,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>66.186999999999998</v>
+        <v>67.632999999999996</v>
       </c>
       <c r="C36">
-        <v>3.782</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,10 +828,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>66.055000000000007</v>
+        <v>67.433999999999997</v>
       </c>
       <c r="C37">
-        <v>4.3860000000000001</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>65.936999999999998</v>
+        <v>67.247</v>
       </c>
       <c r="C38">
-        <v>4.8010000000000002</v>
+        <v>4.7919999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>65.837999999999994</v>
+        <v>67.066000000000003</v>
       </c>
       <c r="C39">
-        <v>4.3760000000000003</v>
+        <v>4.359</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +861,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>65.739999999999995</v>
+        <v>66.897000000000006</v>
       </c>
       <c r="C40">
-        <v>3.4849999999999999</v>
+        <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +872,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>65.649000000000001</v>
+        <v>66.741</v>
       </c>
       <c r="C41">
-        <v>3.1840000000000002</v>
+        <v>3.1779999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +883,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>65.528999999999996</v>
+        <v>66.567999999999998</v>
       </c>
       <c r="C42">
-        <v>3.1619999999999999</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +894,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>65.367999999999995</v>
+        <v>66.373999999999995</v>
       </c>
       <c r="C43">
-        <v>3.274</v>
+        <v>3.2759999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +905,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>65.233000000000004</v>
+        <v>66.209999999999994</v>
       </c>
       <c r="C44">
-        <v>3.4860000000000002</v>
+        <v>3.484</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,10 +916,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>65.129000000000005</v>
+        <v>66.034000000000006</v>
       </c>
       <c r="C45">
-        <v>3.5459999999999998</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -927,10 +927,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.054000000000002</v>
+        <v>65.888999999999996</v>
       </c>
       <c r="C46">
-        <v>3.5310000000000001</v>
+        <v>3.5329999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.001999999999995</v>
+        <v>65.748000000000005</v>
       </c>
       <c r="C47">
-        <v>3.5960000000000001</v>
+        <v>3.5920000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -949,7 +949,7 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>64.914000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="C48">
         <v>3.7530000000000001</v>
@@ -960,7 +960,7 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>64.784000000000006</v>
+        <v>65.356999999999999</v>
       </c>
       <c r="C49">
         <v>4.3339999999999996</v>
@@ -971,10 +971,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>64.643000000000001</v>
+        <v>65.186999999999998</v>
       </c>
       <c r="C50">
-        <v>4.7690000000000001</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,10 +982,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.542000000000002</v>
+        <v>65.033000000000001</v>
       </c>
       <c r="C51">
-        <v>4.3380000000000001</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,10 +993,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.453000000000003</v>
+        <v>64.89</v>
       </c>
       <c r="C52">
-        <v>3.496</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1004,10 +1004,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.370999999999995</v>
+        <v>64.766999999999996</v>
       </c>
       <c r="C53">
-        <v>3.117</v>
+        <v>3.1259999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1015,10 +1015,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.251999999999995</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="C54">
-        <v>3.069</v>
+        <v>3.0819999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.122</v>
+        <v>64.426000000000002</v>
       </c>
       <c r="C55">
-        <v>3.1850000000000001</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,10 +1037,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.025000000000006</v>
+        <v>64.278999999999996</v>
       </c>
       <c r="C56" s="2">
-        <v>3.4279999999999999</v>
+        <v>3.448</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1371,48 +1371,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1707,10 +1665,63 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1727,20 +1738,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE512990-8AE2-45FE-8871-9437531D8117}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A7262D-C242-4708-BF2C-6D13EEE3F697}"/>
   <bookViews>
-    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -520,10 +520,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>81.341999999999999</v>
+        <v>81.438999999999993</v>
       </c>
       <c r="C9">
-        <v>2.8528500000000001</v>
+        <v>2.8713500000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -531,10 +531,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>81.480999999999995</v>
+        <v>81.692999999999998</v>
       </c>
       <c r="C10">
-        <v>2.7669999999999999</v>
+        <v>2.8039999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -542,10 +542,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>79.680999999999997</v>
+        <v>79.878</v>
       </c>
       <c r="C11">
-        <v>2.83</v>
+        <v>2.8620000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>78.212999999999994</v>
+        <v>78.415000000000006</v>
       </c>
       <c r="C12">
-        <v>3.0760000000000001</v>
+        <v>3.0910000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,7 +564,7 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>76.718999999999994</v>
+        <v>76.876000000000005</v>
       </c>
       <c r="C13">
         <v>3.677</v>
@@ -575,10 +575,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>75.512</v>
+        <v>75.599000000000004</v>
       </c>
       <c r="C14">
-        <v>4.1029999999999998</v>
+        <v>4.0990000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +586,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>74.709000000000003</v>
+        <v>74.753</v>
       </c>
       <c r="C15">
-        <v>3.7440000000000002</v>
+        <v>3.742</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>73.894999999999996</v>
+        <v>73.91</v>
       </c>
       <c r="C16">
-        <v>2.976</v>
+        <v>2.9849999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,10 +608,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.225999999999999</v>
+        <v>73.222999999999999</v>
       </c>
       <c r="C17">
-        <v>2.839</v>
+        <v>2.8450000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -619,10 +619,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.716999999999999</v>
+        <v>72.706999999999994</v>
       </c>
       <c r="C18">
-        <v>2.8479999999999999</v>
+        <v>2.8530000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.225999999999999</v>
+        <v>72.218999999999994</v>
       </c>
       <c r="C19">
-        <v>2.9820000000000002</v>
+        <v>2.9870000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +641,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>71.733999999999995</v>
+        <v>71.741</v>
       </c>
       <c r="C20">
-        <v>3.1829999999999998</v>
+        <v>3.1880000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.358999999999995</v>
+        <v>71.382000000000005</v>
       </c>
       <c r="C21">
-        <v>3.2450000000000001</v>
+        <v>3.2509999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -663,10 +663,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>70.992999999999995</v>
+        <v>71.027000000000001</v>
       </c>
       <c r="C22">
-        <v>3.2240000000000002</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,10 +674,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>70.677000000000007</v>
+        <v>70.727000000000004</v>
       </c>
       <c r="C23">
-        <v>3.2949999999999999</v>
+        <v>3.3050000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,10 +685,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.381</v>
+        <v>70.453999999999994</v>
       </c>
       <c r="C24">
-        <v>3.5409999999999999</v>
+        <v>3.5510000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,10 +696,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.051000000000002</v>
+        <v>70.138000000000005</v>
       </c>
       <c r="C25">
-        <v>4.1950000000000003</v>
+        <v>4.194</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>69.762</v>
+        <v>69.866</v>
       </c>
       <c r="C26">
-        <v>4.6470000000000002</v>
+        <v>4.6459999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +718,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.515000000000001</v>
+        <v>69.628</v>
       </c>
       <c r="C27">
-        <v>4.2160000000000002</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +729,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.242999999999995</v>
+        <v>69.367000000000004</v>
       </c>
       <c r="C28">
-        <v>3.4260000000000002</v>
+        <v>3.4289999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +740,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.031000000000006</v>
+        <v>69.164000000000001</v>
       </c>
       <c r="C29">
-        <v>3.1589999999999998</v>
+        <v>3.1619999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>68.814999999999998</v>
+        <v>68.956999999999994</v>
       </c>
       <c r="C30">
-        <v>3.1469999999999998</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +762,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>68.552000000000007</v>
+        <v>68.701999999999998</v>
       </c>
       <c r="C31">
-        <v>3.28</v>
+        <v>3.2829999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,10 +773,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.34</v>
+        <v>68.489999999999995</v>
       </c>
       <c r="C32">
-        <v>3.48</v>
+        <v>3.4820000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,10 +784,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.155000000000001</v>
+        <v>68.305000000000007</v>
       </c>
       <c r="C33">
-        <v>3.5430000000000001</v>
+        <v>3.544</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,7 +795,7 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>67.971000000000004</v>
+        <v>68.123999999999995</v>
       </c>
       <c r="C34">
         <v>3.52</v>
@@ -806,7 +806,7 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>67.808999999999997</v>
+        <v>67.971999999999994</v>
       </c>
       <c r="C35">
         <v>3.5779999999999998</v>
@@ -817,10 +817,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>67.632999999999996</v>
+        <v>67.807000000000002</v>
       </c>
       <c r="C36">
-        <v>3.754</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,10 +828,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.433999999999997</v>
+        <v>67.61</v>
       </c>
       <c r="C37">
-        <v>4.37</v>
+        <v>4.3659999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.247</v>
+        <v>67.417000000000002</v>
       </c>
       <c r="C38">
-        <v>4.7919999999999998</v>
+        <v>4.7869999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,7 +850,7 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.066000000000003</v>
+        <v>67.233000000000004</v>
       </c>
       <c r="C39">
         <v>4.359</v>
@@ -861,10 +861,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>66.897000000000006</v>
+        <v>67.057000000000002</v>
       </c>
       <c r="C40">
-        <v>3.4740000000000002</v>
+        <v>3.476</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +872,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>66.741</v>
+        <v>66.906999999999996</v>
       </c>
       <c r="C41">
-        <v>3.1779999999999999</v>
+        <v>3.1760000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +883,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.567999999999998</v>
+        <v>66.754000000000005</v>
       </c>
       <c r="C42">
-        <v>3.1589999999999998</v>
+        <v>3.1560000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +894,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.373999999999995</v>
+        <v>66.566999999999993</v>
       </c>
       <c r="C43">
-        <v>3.2759999999999998</v>
+        <v>3.2730000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +905,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.209999999999994</v>
+        <v>66.39</v>
       </c>
       <c r="C44">
-        <v>3.484</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,7 +916,7 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.034000000000006</v>
+        <v>66.213999999999999</v>
       </c>
       <c r="C45">
         <v>3.5489999999999999</v>
@@ -927,7 +927,7 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.888999999999996</v>
+        <v>66.069000000000003</v>
       </c>
       <c r="C46">
         <v>3.5329999999999999</v>
@@ -938,7 +938,7 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.748000000000005</v>
+        <v>65.927999999999997</v>
       </c>
       <c r="C47">
         <v>3.5920000000000001</v>
@@ -949,7 +949,7 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.55</v>
+        <v>65.73</v>
       </c>
       <c r="C48">
         <v>3.7530000000000001</v>
@@ -960,7 +960,7 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.356999999999999</v>
+        <v>65.537000000000006</v>
       </c>
       <c r="C49">
         <v>4.3339999999999996</v>
@@ -971,10 +971,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.186999999999998</v>
+        <v>65.367000000000004</v>
       </c>
       <c r="C50">
-        <v>4.7699999999999996</v>
+        <v>4.7709999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,10 +982,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.033000000000001</v>
+        <v>65.212999999999994</v>
       </c>
       <c r="C51">
-        <v>4.3499999999999996</v>
+        <v>4.351</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,7 +993,7 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.89</v>
+        <v>65.069999999999993</v>
       </c>
       <c r="C52">
         <v>3.5</v>
@@ -1004,7 +1004,7 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.766999999999996</v>
+        <v>64.947000000000003</v>
       </c>
       <c r="C53">
         <v>3.1259999999999999</v>
@@ -1015,7 +1015,7 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.599999999999994</v>
+        <v>64.78</v>
       </c>
       <c r="C54">
         <v>3.0819999999999999</v>
@@ -1026,7 +1026,7 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.426000000000002</v>
+        <v>64.605999999999995</v>
       </c>
       <c r="C55">
         <v>3.202</v>
@@ -1037,10 +1037,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.278999999999996</v>
+        <v>64.459000000000003</v>
       </c>
       <c r="C56" s="2">
-        <v>3.448</v>
+        <v>3.4470000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1371,6 +1371,39 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1665,39 +1698,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1708,6 +1708,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1726,17 +1737,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A7262D-C242-4708-BF2C-6D13EEE3F697}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A93610-97A3-444B-B958-0BB7E68A48B5}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -520,10 +520,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>81.438999999999993</v>
+        <v>80.902000000000001</v>
       </c>
       <c r="C9">
-        <v>2.8713500000000001</v>
+        <v>2.8358500000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -531,10 +531,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>81.692999999999998</v>
+        <v>81.078999999999994</v>
       </c>
       <c r="C10">
-        <v>2.8039999999999998</v>
+        <v>2.7330000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -542,10 +542,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>79.878</v>
+        <v>79.515000000000001</v>
       </c>
       <c r="C11">
-        <v>2.8620000000000001</v>
+        <v>2.7850000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>78.415000000000006</v>
+        <v>78.13</v>
       </c>
       <c r="C12">
-        <v>3.0910000000000002</v>
+        <v>2.9860000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,10 +564,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>76.876000000000005</v>
+        <v>76.659000000000006</v>
       </c>
       <c r="C13">
-        <v>3.677</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +575,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>75.599000000000004</v>
+        <v>75.451999999999998</v>
       </c>
       <c r="C14">
-        <v>4.0990000000000002</v>
+        <v>3.9609999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +586,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>74.753</v>
+        <v>74.647000000000006</v>
       </c>
       <c r="C15">
-        <v>3.742</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>73.91</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="C16">
-        <v>2.9849999999999999</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,10 +608,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.222999999999999</v>
+        <v>73.135999999999996</v>
       </c>
       <c r="C17">
-        <v>2.8450000000000002</v>
+        <v>2.8079999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -619,10 +619,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.706999999999994</v>
+        <v>72.63</v>
       </c>
       <c r="C18">
-        <v>2.8530000000000002</v>
+        <v>2.8210000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.218999999999994</v>
+        <v>72.153999999999996</v>
       </c>
       <c r="C19">
-        <v>2.9870000000000001</v>
+        <v>2.9630000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +641,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>71.741</v>
+        <v>71.691000000000003</v>
       </c>
       <c r="C20">
-        <v>3.1880000000000002</v>
+        <v>3.1659999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.382000000000005</v>
+        <v>71.331999999999994</v>
       </c>
       <c r="C21">
-        <v>3.2509999999999999</v>
+        <v>3.2320000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -663,10 +663,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>71.027000000000001</v>
+        <v>70.977000000000004</v>
       </c>
       <c r="C22">
-        <v>3.23</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,10 +674,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>70.727000000000004</v>
+        <v>70.686999999999998</v>
       </c>
       <c r="C23">
-        <v>3.3050000000000002</v>
+        <v>3.2909999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,10 +685,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.453999999999994</v>
+        <v>70.436999999999998</v>
       </c>
       <c r="C24">
-        <v>3.5510000000000002</v>
+        <v>3.5409999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,10 +696,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.138000000000005</v>
+        <v>70.125</v>
       </c>
       <c r="C25">
-        <v>4.194</v>
+        <v>4.1879999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>69.866</v>
+        <v>69.852999999999994</v>
       </c>
       <c r="C26">
-        <v>4.6459999999999999</v>
+        <v>4.6369999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +718,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.628</v>
+        <v>69.632999999999996</v>
       </c>
       <c r="C27">
-        <v>4.22</v>
+        <v>4.2069999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +729,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.367000000000004</v>
+        <v>69.387</v>
       </c>
       <c r="C28">
-        <v>3.4289999999999998</v>
+        <v>3.419</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +740,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.164000000000001</v>
+        <v>69.186999999999998</v>
       </c>
       <c r="C29">
-        <v>3.1619999999999999</v>
+        <v>3.1680000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>68.956999999999994</v>
+        <v>68.989999999999995</v>
       </c>
       <c r="C30">
-        <v>3.149</v>
+        <v>3.1579999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +762,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>68.701999999999998</v>
+        <v>68.75</v>
       </c>
       <c r="C31">
-        <v>3.2829999999999999</v>
+        <v>3.2959999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,10 +773,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.489999999999995</v>
+        <v>68.55</v>
       </c>
       <c r="C32">
-        <v>3.4820000000000002</v>
+        <v>3.4929999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,10 +784,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.305000000000007</v>
+        <v>68.361999999999995</v>
       </c>
       <c r="C33">
-        <v>3.544</v>
+        <v>3.5579999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.123999999999995</v>
+        <v>68.177999999999997</v>
       </c>
       <c r="C34">
-        <v>3.52</v>
+        <v>3.5329999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +806,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>67.971999999999994</v>
+        <v>68.031999999999996</v>
       </c>
       <c r="C35">
-        <v>3.5779999999999998</v>
+        <v>3.5880000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,10 +817,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>67.807000000000002</v>
+        <v>67.867000000000004</v>
       </c>
       <c r="C36">
-        <v>3.75</v>
+        <v>3.7530000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,10 +828,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.61</v>
+        <v>67.674000000000007</v>
       </c>
       <c r="C37">
-        <v>4.3659999999999997</v>
+        <v>4.3579999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.417000000000002</v>
+        <v>67.497</v>
       </c>
       <c r="C38">
-        <v>4.7869999999999999</v>
+        <v>4.7779999999999996</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.233000000000004</v>
+        <v>67.343000000000004</v>
       </c>
       <c r="C39">
-        <v>4.359</v>
+        <v>4.3460000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +861,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.057000000000002</v>
+        <v>67.19</v>
       </c>
       <c r="C40">
-        <v>3.476</v>
+        <v>3.464</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +872,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>66.906999999999996</v>
+        <v>67.043999999999997</v>
       </c>
       <c r="C41">
-        <v>3.1760000000000002</v>
+        <v>3.1659999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +883,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.754000000000005</v>
+        <v>66.881</v>
       </c>
       <c r="C42">
-        <v>3.1560000000000001</v>
+        <v>3.1469999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +894,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.566999999999993</v>
+        <v>66.697999999999993</v>
       </c>
       <c r="C43">
-        <v>3.2730000000000001</v>
+        <v>3.266</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +905,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.39</v>
+        <v>66.546999999999997</v>
       </c>
       <c r="C44">
-        <v>3.48</v>
+        <v>3.472</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,10 +916,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.213999999999999</v>
+        <v>66.388000000000005</v>
       </c>
       <c r="C45">
-        <v>3.5489999999999999</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -927,10 +927,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.069000000000003</v>
+        <v>66.245999999999995</v>
       </c>
       <c r="C46">
-        <v>3.5329999999999999</v>
+        <v>3.5219999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.927999999999997</v>
+        <v>66.106999999999999</v>
       </c>
       <c r="C47">
-        <v>3.5920000000000001</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -949,10 +949,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.73</v>
+        <v>65.941000000000003</v>
       </c>
       <c r="C48">
-        <v>3.7530000000000001</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +960,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.537000000000006</v>
+        <v>65.763999999999996</v>
       </c>
       <c r="C49">
-        <v>4.3339999999999996</v>
+        <v>4.3179999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,10 +971,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.367000000000004</v>
+        <v>65.593000000000004</v>
       </c>
       <c r="C50">
-        <v>4.7709999999999999</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,10 +982,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.212999999999994</v>
+        <v>65.456000000000003</v>
       </c>
       <c r="C51">
-        <v>4.351</v>
+        <v>4.3209999999999997</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,10 +993,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.069999999999993</v>
+        <v>65.322999999999993</v>
       </c>
       <c r="C52">
-        <v>3.5</v>
+        <v>3.4660000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1004,10 +1004,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.947000000000003</v>
+        <v>65.209999999999994</v>
       </c>
       <c r="C53">
-        <v>3.1259999999999999</v>
+        <v>3.0920000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1015,10 +1015,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.78</v>
+        <v>65.052999999999997</v>
       </c>
       <c r="C54">
-        <v>3.0819999999999999</v>
+        <v>3.0489999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.605999999999995</v>
+        <v>64.885999999999996</v>
       </c>
       <c r="C55">
-        <v>3.202</v>
+        <v>3.1680000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,10 +1037,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.459000000000003</v>
+        <v>64.739000000000004</v>
       </c>
       <c r="C56" s="2">
-        <v>3.4470000000000001</v>
+        <v>3.4089999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1371,36 +1371,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1699,21 +1675,42 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1738,9 +1735,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A93610-97A3-444B-B958-0BB7E68A48B5}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7A5320-B7EC-4BDF-915B-B460ABBF2610}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterate="1"/>
+  <calcPr calcId="191029" iterate="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -520,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>80.902000000000001</v>
+        <v>82.058999999999997</v>
       </c>
       <c r="C9">
-        <v>2.8358500000000002</v>
+        <v>2.8143500000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -531,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>81.078999999999994</v>
+        <v>83.36</v>
       </c>
       <c r="C10">
-        <v>2.7330000000000001</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -542,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>79.515000000000001</v>
+        <v>81.834999999999994</v>
       </c>
       <c r="C11">
-        <v>2.7850000000000001</v>
+        <v>2.7290000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>78.13</v>
+        <v>80.454999999999998</v>
       </c>
       <c r="C12">
-        <v>2.9860000000000002</v>
+        <v>2.9209999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>76.659000000000006</v>
+        <v>78.906999999999996</v>
       </c>
       <c r="C13">
-        <v>3.5489999999999999</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>75.451999999999998</v>
+        <v>77.584000000000003</v>
       </c>
       <c r="C14">
-        <v>3.9609999999999999</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>74.647000000000006</v>
+        <v>76.671999999999997</v>
       </c>
       <c r="C15">
-        <v>3.633</v>
+        <v>3.577</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>73.819999999999993</v>
+        <v>75.716999999999999</v>
       </c>
       <c r="C16">
-        <v>2.93</v>
+        <v>2.8940000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.135999999999996</v>
+        <v>74.914000000000001</v>
       </c>
       <c r="C17">
-        <v>2.8079999999999998</v>
+        <v>2.774</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -619,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.63</v>
+        <v>74.325999999999993</v>
       </c>
       <c r="C18">
-        <v>2.8210000000000002</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.153999999999996</v>
+        <v>73.771000000000001</v>
       </c>
       <c r="C19">
-        <v>2.9630000000000001</v>
+        <v>2.9329999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>71.691000000000003</v>
+        <v>73.228999999999999</v>
       </c>
       <c r="C20">
-        <v>3.1659999999999999</v>
+        <v>3.1379999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.331999999999994</v>
+        <v>72.816000000000003</v>
       </c>
       <c r="C21">
-        <v>3.2320000000000002</v>
+        <v>3.206</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -663,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>70.977000000000004</v>
+        <v>72.412999999999997</v>
       </c>
       <c r="C22">
-        <v>3.214</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>70.686999999999998</v>
+        <v>72.069999999999993</v>
       </c>
       <c r="C23">
-        <v>3.2909999999999999</v>
+        <v>3.266</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.436999999999998</v>
+        <v>71.753</v>
       </c>
       <c r="C24">
-        <v>3.5409999999999999</v>
+        <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.125</v>
+        <v>71.394000000000005</v>
       </c>
       <c r="C25">
-        <v>4.1879999999999997</v>
+        <v>4.1719999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>69.852999999999994</v>
+        <v>71.088999999999999</v>
       </c>
       <c r="C26">
-        <v>4.6369999999999996</v>
+        <v>4.6239999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.632999999999996</v>
+        <v>70.832999999999998</v>
       </c>
       <c r="C27">
-        <v>4.2069999999999999</v>
+        <v>4.1929999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.387</v>
+        <v>70.546999999999997</v>
       </c>
       <c r="C28">
-        <v>3.419</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.186999999999998</v>
+        <v>70.316999999999993</v>
       </c>
       <c r="C29">
-        <v>3.1680000000000001</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>68.989999999999995</v>
+        <v>70.091999999999999</v>
       </c>
       <c r="C30">
-        <v>3.1579999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>68.75</v>
+        <v>69.819000000000003</v>
       </c>
       <c r="C31">
-        <v>3.2959999999999998</v>
+        <v>3.2909999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.55</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="C32">
-        <v>3.4929999999999999</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.361999999999995</v>
+        <v>69.409000000000006</v>
       </c>
       <c r="C33">
-        <v>3.5579999999999998</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.177999999999997</v>
+        <v>69.210999999999999</v>
       </c>
       <c r="C34">
-        <v>3.5329999999999999</v>
+        <v>3.524</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.031999999999996</v>
+        <v>69.046000000000006</v>
       </c>
       <c r="C35">
-        <v>3.5880000000000001</v>
+        <v>3.5760000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>67.867000000000004</v>
+        <v>68.86</v>
       </c>
       <c r="C36">
-        <v>3.7530000000000001</v>
+        <v>3.7389999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.674000000000007</v>
+        <v>68.647000000000006</v>
       </c>
       <c r="C37">
-        <v>4.3579999999999997</v>
+        <v>4.343</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.497</v>
+        <v>68.447000000000003</v>
       </c>
       <c r="C38">
-        <v>4.7779999999999996</v>
+        <v>4.7640000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.343000000000004</v>
+        <v>68.263000000000005</v>
       </c>
       <c r="C39">
-        <v>4.3460000000000001</v>
+        <v>4.3319999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.19</v>
+        <v>68.082999999999998</v>
       </c>
       <c r="C40">
-        <v>3.464</v>
+        <v>3.4510000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.043999999999997</v>
+        <v>67.924000000000007</v>
       </c>
       <c r="C41">
-        <v>3.1659999999999999</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.881</v>
+        <v>67.757999999999996</v>
       </c>
       <c r="C42">
-        <v>3.1469999999999998</v>
+        <v>3.1379999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.697999999999993</v>
+        <v>67.557000000000002</v>
       </c>
       <c r="C43">
-        <v>3.266</v>
+        <v>3.2570000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.546999999999997</v>
+        <v>67.38</v>
       </c>
       <c r="C44">
-        <v>3.472</v>
+        <v>3.4620000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.388000000000005</v>
+        <v>67.203999999999994</v>
       </c>
       <c r="C45">
-        <v>3.5390000000000001</v>
+        <v>3.5289999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -927,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.245999999999995</v>
+        <v>67.055999999999997</v>
       </c>
       <c r="C46">
-        <v>3.5219999999999998</v>
+        <v>3.5129999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -938,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.106999999999999</v>
+        <v>66.911000000000001</v>
       </c>
       <c r="C47">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -949,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.941000000000003</v>
+        <v>66.724000000000004</v>
       </c>
       <c r="C48">
-        <v>3.74</v>
+        <v>3.7269999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.763999999999996</v>
+        <v>66.527000000000001</v>
       </c>
       <c r="C49">
-        <v>4.3179999999999996</v>
+        <v>4.306</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.593000000000004</v>
+        <v>66.34</v>
       </c>
       <c r="C50">
-        <v>4.75</v>
+        <v>4.7380000000000004</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.456000000000003</v>
+        <v>66.192999999999998</v>
       </c>
       <c r="C51">
-        <v>4.3209999999999997</v>
+        <v>4.3109999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.322999999999993</v>
+        <v>66.043000000000006</v>
       </c>
       <c r="C52">
-        <v>3.4660000000000002</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1004,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.209999999999994</v>
+        <v>65.903999999999996</v>
       </c>
       <c r="C53">
-        <v>3.0920000000000001</v>
+        <v>3.0830000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1015,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.052999999999997</v>
+        <v>65.73</v>
       </c>
       <c r="C54">
-        <v>3.0489999999999999</v>
+        <v>3.0379999999999998</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.885999999999996</v>
+        <v>65.552999999999997</v>
       </c>
       <c r="C55">
-        <v>3.1680000000000001</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.739000000000004</v>
+        <v>65.396000000000001</v>
       </c>
       <c r="C56" s="2">
-        <v>3.4089999999999998</v>
+        <v>3.3969999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1371,15 +1384,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1674,6 +1678,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1708,14 +1721,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1734,6 +1739,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7A5320-B7EC-4BDF-915B-B460ABBF2610}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D39A775-5BBE-4BA7-9592-FC345B7EB51D}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.058999999999997</v>
+        <v>82.227999999999994</v>
       </c>
       <c r="C9">
-        <v>2.8143500000000001</v>
+        <v>2.8573499999999998</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>83.36</v>
+        <v>83.677000000000007</v>
       </c>
       <c r="C10">
-        <v>2.69</v>
+        <v>2.7759999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>81.834999999999994</v>
+        <v>82.167000000000002</v>
       </c>
       <c r="C11">
-        <v>2.7290000000000001</v>
+        <v>2.8029999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>80.454999999999998</v>
+        <v>80.832999999999998</v>
       </c>
       <c r="C12">
-        <v>2.9209999999999998</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>78.906999999999996</v>
+        <v>79.307000000000002</v>
       </c>
       <c r="C13">
-        <v>3.488</v>
+        <v>3.5419999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>77.584000000000003</v>
+        <v>77.972999999999999</v>
       </c>
       <c r="C14">
-        <v>3.9</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>76.671999999999997</v>
+        <v>77.036000000000001</v>
       </c>
       <c r="C15">
-        <v>3.577</v>
+        <v>3.617</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>75.716999999999999</v>
+        <v>76.052000000000007</v>
       </c>
       <c r="C16">
-        <v>2.8940000000000001</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>74.914000000000001</v>
+        <v>75.225999999999999</v>
       </c>
       <c r="C17">
-        <v>2.774</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.325999999999993</v>
+        <v>74.617000000000004</v>
       </c>
       <c r="C18">
-        <v>2.79</v>
+        <v>2.8170000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>73.771000000000001</v>
+        <v>74.036000000000001</v>
       </c>
       <c r="C19">
-        <v>2.9329999999999998</v>
+        <v>2.9580000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>73.228999999999999</v>
+        <v>73.471000000000004</v>
       </c>
       <c r="C20">
-        <v>3.1379999999999999</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>72.816000000000003</v>
+        <v>73.043000000000006</v>
       </c>
       <c r="C21">
-        <v>3.206</v>
+        <v>3.2269999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.412999999999997</v>
+        <v>72.623000000000005</v>
       </c>
       <c r="C22">
-        <v>3.19</v>
+        <v>3.2120000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.069999999999993</v>
+        <v>72.260000000000005</v>
       </c>
       <c r="C23">
-        <v>3.266</v>
+        <v>3.2890000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>71.753</v>
+        <v>71.94</v>
       </c>
       <c r="C24">
-        <v>3.5249999999999999</v>
+        <v>3.5449999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.394000000000005</v>
+        <v>71.569999999999993</v>
       </c>
       <c r="C25">
-        <v>4.1719999999999997</v>
+        <v>4.1890000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.088999999999999</v>
+        <v>71.251999999999995</v>
       </c>
       <c r="C26">
-        <v>4.6239999999999997</v>
+        <v>4.633</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.832999999999998</v>
+        <v>70.977999999999994</v>
       </c>
       <c r="C27">
-        <v>4.1929999999999996</v>
+        <v>4.1989999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.546999999999997</v>
+        <v>70.677000000000007</v>
       </c>
       <c r="C28">
-        <v>3.41</v>
+        <v>3.4180000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.316999999999993</v>
+        <v>70.444000000000003</v>
       </c>
       <c r="C29">
-        <v>3.1589999999999998</v>
+        <v>3.1669999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.091999999999999</v>
+        <v>70.209000000000003</v>
       </c>
       <c r="C30">
-        <v>3.1509999999999998</v>
+        <v>3.1619999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.819000000000003</v>
+        <v>69.924999999999997</v>
       </c>
       <c r="C31">
-        <v>3.2909999999999999</v>
+        <v>3.3050000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.599999999999994</v>
+        <v>69.692999999999998</v>
       </c>
       <c r="C32">
-        <v>3.488</v>
+        <v>3.4990000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.409000000000006</v>
+        <v>69.489000000000004</v>
       </c>
       <c r="C33">
-        <v>3.55</v>
+        <v>3.5619999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.210999999999999</v>
+        <v>69.284000000000006</v>
       </c>
       <c r="C34">
-        <v>3.524</v>
+        <v>3.5350000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.046000000000006</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="C35">
-        <v>3.5760000000000001</v>
+        <v>3.585</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.86</v>
+        <v>68.893000000000001</v>
       </c>
       <c r="C36">
-        <v>3.7389999999999999</v>
+        <v>3.7440000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.647000000000006</v>
+        <v>68.662999999999997</v>
       </c>
       <c r="C37">
-        <v>4.343</v>
+        <v>4.3460000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.447000000000003</v>
+        <v>68.456999999999994</v>
       </c>
       <c r="C38">
-        <v>4.7640000000000002</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.263000000000005</v>
+        <v>68.272999999999996</v>
       </c>
       <c r="C39">
-        <v>4.3319999999999999</v>
+        <v>4.3380000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.082999999999998</v>
+        <v>68.093000000000004</v>
       </c>
       <c r="C40">
-        <v>3.4510000000000001</v>
+        <v>3.4529999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.924000000000007</v>
+        <v>67.929000000000002</v>
       </c>
       <c r="C41">
-        <v>3.157</v>
+        <v>3.153</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.757999999999996</v>
+        <v>67.745000000000005</v>
       </c>
       <c r="C42">
-        <v>3.1379999999999999</v>
+        <v>3.1339999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.557000000000002</v>
+        <v>67.534000000000006</v>
       </c>
       <c r="C43">
-        <v>3.2570000000000001</v>
+        <v>3.2549999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.38</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="C44">
-        <v>3.4620000000000002</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.203999999999994</v>
+        <v>67.171000000000006</v>
       </c>
       <c r="C45">
-        <v>3.5289999999999999</v>
+        <v>3.5230000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.055999999999997</v>
+        <v>67.013000000000005</v>
       </c>
       <c r="C46">
-        <v>3.5129999999999999</v>
+        <v>3.5070000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.911000000000001</v>
+        <v>66.867000000000004</v>
       </c>
       <c r="C47">
-        <v>3.57</v>
+        <v>3.5659999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.724000000000004</v>
+        <v>66.697999999999993</v>
       </c>
       <c r="C48">
-        <v>3.7269999999999999</v>
+        <v>3.722</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.527000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="C49">
-        <v>4.306</v>
+        <v>4.3019999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.34</v>
+        <v>66.3</v>
       </c>
       <c r="C50">
-        <v>4.7380000000000004</v>
+        <v>4.7389999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.192999999999998</v>
+        <v>66.153000000000006</v>
       </c>
       <c r="C51">
-        <v>4.3109999999999999</v>
+        <v>4.3129999999999997</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,7 +1006,7 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>66.043000000000006</v>
+        <v>66</v>
       </c>
       <c r="C52">
         <v>3.46</v>
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.903999999999996</v>
+        <v>65.853999999999999</v>
       </c>
       <c r="C53">
-        <v>3.0830000000000002</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.73</v>
+        <v>65.676000000000002</v>
       </c>
       <c r="C54">
-        <v>3.0379999999999998</v>
+        <v>3.032</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.552999999999997</v>
+        <v>65.492999999999995</v>
       </c>
       <c r="C55">
-        <v>3.157</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>65.396000000000001</v>
+        <v>65.332999999999998</v>
       </c>
       <c r="C56" s="2">
-        <v>3.3969999999999998</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1384,6 +1384,48 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1678,49 +1720,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1737,23 +1756,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D39A775-5BBE-4BA7-9592-FC345B7EB51D}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B693BAA-3AC2-4ADB-B298-92FDE4CDA8F8}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -533,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.227999999999994</v>
+        <v>83.331000000000003</v>
       </c>
       <c r="C9">
-        <v>2.8573499999999998</v>
+        <v>2.8358500000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>83.677000000000007</v>
+        <v>86.266999999999996</v>
       </c>
       <c r="C10">
-        <v>2.7759999999999998</v>
+        <v>2.7330000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>82.167000000000002</v>
+        <v>84.063999999999993</v>
       </c>
       <c r="C11">
-        <v>2.8029999999999999</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>80.832999999999998</v>
+        <v>82.194999999999993</v>
       </c>
       <c r="C12">
-        <v>2.99</v>
+        <v>2.9249999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>79.307000000000002</v>
+        <v>80.254999999999995</v>
       </c>
       <c r="C13">
-        <v>3.5419999999999998</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>77.972999999999999</v>
+        <v>78.653000000000006</v>
       </c>
       <c r="C14">
-        <v>3.952</v>
+        <v>3.8780000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>77.036000000000001</v>
+        <v>77.566000000000003</v>
       </c>
       <c r="C15">
-        <v>3.617</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>76.052000000000007</v>
+        <v>76.45</v>
       </c>
       <c r="C16">
-        <v>2.92</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>75.225999999999999</v>
+        <v>75.545000000000002</v>
       </c>
       <c r="C17">
-        <v>2.8</v>
+        <v>2.7589999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.617000000000004</v>
+        <v>74.888000000000005</v>
       </c>
       <c r="C18">
-        <v>2.8170000000000002</v>
+        <v>2.7770000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>74.036000000000001</v>
+        <v>74.28</v>
       </c>
       <c r="C19">
-        <v>2.9580000000000002</v>
+        <v>2.9169999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>73.471000000000004</v>
+        <v>73.692999999999998</v>
       </c>
       <c r="C20">
-        <v>3.1589999999999998</v>
+        <v>3.121</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>73.043000000000006</v>
+        <v>73.247</v>
       </c>
       <c r="C21">
-        <v>3.2269999999999999</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.623000000000005</v>
+        <v>72.813000000000002</v>
       </c>
       <c r="C22">
-        <v>3.2120000000000002</v>
+        <v>3.1749999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.260000000000005</v>
+        <v>72.45</v>
       </c>
       <c r="C23">
-        <v>3.2890000000000001</v>
+        <v>3.254</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>71.94</v>
+        <v>72.126999999999995</v>
       </c>
       <c r="C24">
-        <v>3.5449999999999999</v>
+        <v>3.5209999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.569999999999993</v>
+        <v>71.745999999999995</v>
       </c>
       <c r="C25">
-        <v>4.1890000000000001</v>
+        <v>4.1719999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.251999999999995</v>
+        <v>71.421999999999997</v>
       </c>
       <c r="C26">
-        <v>4.633</v>
+        <v>4.625</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.977999999999994</v>
+        <v>71.144999999999996</v>
       </c>
       <c r="C27">
-        <v>4.1989999999999998</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.677000000000007</v>
+        <v>70.83</v>
       </c>
       <c r="C28">
-        <v>3.4180000000000001</v>
+        <v>3.4129999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.444000000000003</v>
+        <v>70.584000000000003</v>
       </c>
       <c r="C29">
-        <v>3.1669999999999998</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.209000000000003</v>
+        <v>70.349000000000004</v>
       </c>
       <c r="C30">
-        <v>3.1619999999999999</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.924999999999997</v>
+        <v>70.064999999999998</v>
       </c>
       <c r="C31">
-        <v>3.3050000000000002</v>
+        <v>3.3039999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.692999999999998</v>
+        <v>69.832999999999998</v>
       </c>
       <c r="C32">
-        <v>3.4990000000000001</v>
+        <v>3.5009999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.489000000000004</v>
+        <v>69.629000000000005</v>
       </c>
       <c r="C33">
-        <v>3.5619999999999998</v>
+        <v>3.5659999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.284000000000006</v>
+        <v>69.42</v>
       </c>
       <c r="C34">
-        <v>3.5350000000000001</v>
+        <v>3.5419999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.099999999999994</v>
+        <v>69.236000000000004</v>
       </c>
       <c r="C35">
-        <v>3.585</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.893000000000001</v>
+        <v>69.046999999999997</v>
       </c>
       <c r="C36">
-        <v>3.7440000000000002</v>
+        <v>3.7559999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,7 +841,7 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.662999999999997</v>
+        <v>68.819999999999993</v>
       </c>
       <c r="C37">
         <v>4.3460000000000001</v>
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.456999999999994</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="C38">
-        <v>4.7699999999999996</v>
+        <v>4.7690000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.272999999999996</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="C39">
-        <v>4.3380000000000001</v>
+        <v>4.3360000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.093000000000004</v>
+        <v>68.209999999999994</v>
       </c>
       <c r="C40">
-        <v>3.4529999999999998</v>
+        <v>3.4510000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,7 +885,7 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.929000000000002</v>
+        <v>68.039000000000001</v>
       </c>
       <c r="C41">
         <v>3.153</v>
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.745000000000005</v>
+        <v>67.852999999999994</v>
       </c>
       <c r="C42">
-        <v>3.1339999999999999</v>
+        <v>3.1349999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.534000000000006</v>
+        <v>67.63</v>
       </c>
       <c r="C43">
-        <v>3.2549999999999999</v>
+        <v>3.2559999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,7 +918,7 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.349999999999994</v>
+        <v>67.436999999999998</v>
       </c>
       <c r="C44">
         <v>3.456</v>
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.171000000000006</v>
+        <v>67.251000000000005</v>
       </c>
       <c r="C45">
-        <v>3.5230000000000001</v>
+        <v>3.524</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.013000000000005</v>
+        <v>67.088999999999999</v>
       </c>
       <c r="C46">
-        <v>3.5070000000000001</v>
+        <v>3.508</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.867000000000004</v>
+        <v>66.933999999999997</v>
       </c>
       <c r="C47">
-        <v>3.5659999999999998</v>
+        <v>3.5640000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.697999999999993</v>
+        <v>66.754000000000005</v>
       </c>
       <c r="C48">
-        <v>3.722</v>
+        <v>3.7210000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.5</v>
+        <v>66.55</v>
       </c>
       <c r="C49">
-        <v>4.3019999999999996</v>
+        <v>4.298</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.3</v>
+        <v>66.346999999999994</v>
       </c>
       <c r="C50">
         <v>4.7389999999999999</v>
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.153000000000006</v>
+        <v>66.188999999999993</v>
       </c>
       <c r="C51">
-        <v>4.3129999999999997</v>
+        <v>4.3159999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>66</v>
+        <v>66.03</v>
       </c>
       <c r="C52">
-        <v>3.46</v>
+        <v>3.464</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.853999999999999</v>
+        <v>65.881</v>
       </c>
       <c r="C53">
-        <v>3.08</v>
+        <v>3.0819999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.676000000000002</v>
+        <v>65.692999999999998</v>
       </c>
       <c r="C54">
-        <v>3.032</v>
+        <v>3.036</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.492999999999995</v>
+        <v>65.498999999999995</v>
       </c>
       <c r="C55">
-        <v>3.1509999999999998</v>
+        <v>3.1539999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>65.332999999999998</v>
       </c>
       <c r="C56" s="2">
-        <v>3.39</v>
+        <v>3.391</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1384,48 +1384,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1720,26 +1678,49 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1756,4 +1737,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B693BAA-3AC2-4ADB-B298-92FDE4CDA8F8}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83C0C6E3-2C11-4C5B-AB77-97C6B55BC32B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -533,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>83.331000000000003</v>
+        <v>83.408000000000001</v>
       </c>
       <c r="C9">
-        <v>2.8358500000000002</v>
+        <v>2.8558500000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>86.266999999999996</v>
+        <v>86.516999999999996</v>
       </c>
       <c r="C10">
-        <v>2.7330000000000001</v>
+        <v>2.7730000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>84.063999999999993</v>
+        <v>84.382000000000005</v>
       </c>
       <c r="C11">
-        <v>2.76</v>
+        <v>2.8109999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>82.194999999999993</v>
+        <v>82.528000000000006</v>
       </c>
       <c r="C12">
-        <v>2.9249999999999998</v>
+        <v>2.9740000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>80.254999999999995</v>
+        <v>80.515000000000001</v>
       </c>
       <c r="C13">
-        <v>3.47</v>
+        <v>3.4969999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>78.653000000000006</v>
+        <v>78.853999999999999</v>
       </c>
       <c r="C14">
-        <v>3.8780000000000001</v>
+        <v>3.8959999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>77.566000000000003</v>
+        <v>77.73</v>
       </c>
       <c r="C15">
-        <v>3.5489999999999999</v>
+        <v>3.5670000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>76.45</v>
+        <v>76.581999999999994</v>
       </c>
       <c r="C16">
-        <v>2.883</v>
+        <v>2.8959999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>75.545000000000002</v>
+        <v>75.644000000000005</v>
       </c>
       <c r="C17">
-        <v>2.7589999999999999</v>
+        <v>2.7679999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.888000000000005</v>
+        <v>74.965000000000003</v>
       </c>
       <c r="C18">
-        <v>2.7770000000000001</v>
+        <v>2.7850000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>74.28</v>
+        <v>74.343999999999994</v>
       </c>
       <c r="C19">
-        <v>2.9169999999999998</v>
+        <v>2.9260000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>73.692999999999998</v>
+        <v>73.736000000000004</v>
       </c>
       <c r="C20">
-        <v>3.121</v>
+        <v>3.1309999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>73.247</v>
+        <v>73.277000000000001</v>
       </c>
       <c r="C21">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.813000000000002</v>
+        <v>72.84</v>
       </c>
       <c r="C22">
-        <v>3.1749999999999998</v>
+        <v>3.1859999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.45</v>
+        <v>72.462999999999994</v>
       </c>
       <c r="C23">
-        <v>3.254</v>
+        <v>3.2669999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -701,7 +701,7 @@
         <v>72.126999999999995</v>
       </c>
       <c r="C24">
-        <v>3.5209999999999999</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -712,7 +712,7 @@
         <v>71.745999999999995</v>
       </c>
       <c r="C25">
-        <v>4.1719999999999997</v>
+        <v>4.1909999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.421999999999997</v>
+        <v>71.418000000000006</v>
       </c>
       <c r="C26">
-        <v>4.625</v>
+        <v>4.6379999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>71.144999999999996</v>
+        <v>71.135000000000005</v>
       </c>
       <c r="C27">
-        <v>4.1900000000000004</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.83</v>
+        <v>70.822999999999993</v>
       </c>
       <c r="C28">
-        <v>3.4129999999999998</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.584000000000003</v>
+        <v>70.581000000000003</v>
       </c>
       <c r="C29">
-        <v>3.165</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.349000000000004</v>
+        <v>70.338999999999999</v>
       </c>
       <c r="C30">
-        <v>3.1589999999999998</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.064999999999998</v>
+        <v>70.055000000000007</v>
       </c>
       <c r="C31">
-        <v>3.3039999999999998</v>
+        <v>3.3159999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.832999999999998</v>
+        <v>69.819999999999993</v>
       </c>
       <c r="C32">
-        <v>3.5009999999999999</v>
+        <v>3.512</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.629000000000005</v>
+        <v>69.602999999999994</v>
       </c>
       <c r="C33">
-        <v>3.5659999999999998</v>
+        <v>3.5750000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.42</v>
+        <v>69.384</v>
       </c>
       <c r="C34">
-        <v>3.5419999999999998</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.236000000000004</v>
+        <v>69.203000000000003</v>
       </c>
       <c r="C35">
-        <v>3.593</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.046999999999997</v>
+        <v>69.003</v>
       </c>
       <c r="C36">
-        <v>3.7559999999999998</v>
+        <v>3.7650000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.819999999999993</v>
+        <v>68.772999999999996</v>
       </c>
       <c r="C37">
-        <v>4.3460000000000001</v>
+        <v>4.3559999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.599999999999994</v>
+        <v>68.56</v>
       </c>
       <c r="C38">
-        <v>4.7690000000000001</v>
+        <v>4.7809999999999997</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.400000000000006</v>
+        <v>68.36</v>
       </c>
       <c r="C39">
-        <v>4.3360000000000003</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.209999999999994</v>
+        <v>68.167000000000002</v>
       </c>
       <c r="C40">
-        <v>3.4510000000000001</v>
+        <v>3.4620000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>68.039000000000001</v>
+        <v>67.989000000000004</v>
       </c>
       <c r="C41">
-        <v>3.153</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.852999999999994</v>
+        <v>67.805000000000007</v>
       </c>
       <c r="C42">
-        <v>3.1349999999999998</v>
+        <v>3.1469999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.63</v>
+        <v>67.593999999999994</v>
       </c>
       <c r="C43">
-        <v>3.2559999999999998</v>
+        <v>3.2679999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.436999999999998</v>
+        <v>67.406999999999996</v>
       </c>
       <c r="C44">
-        <v>3.456</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.251000000000005</v>
+        <v>67.221000000000004</v>
       </c>
       <c r="C45">
-        <v>3.524</v>
+        <v>3.5350000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.088999999999999</v>
+        <v>67.058999999999997</v>
       </c>
       <c r="C46">
-        <v>3.508</v>
+        <v>3.5190000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.933999999999997</v>
+        <v>66.894999999999996</v>
       </c>
       <c r="C47">
-        <v>3.5640000000000001</v>
+        <v>3.577</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.754000000000005</v>
+        <v>66.686000000000007</v>
       </c>
       <c r="C48">
-        <v>3.7210000000000001</v>
+        <v>3.734</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.55</v>
+        <v>66.477000000000004</v>
       </c>
       <c r="C49">
-        <v>4.298</v>
+        <v>4.3079999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.346999999999994</v>
+        <v>66.283000000000001</v>
       </c>
       <c r="C50">
-        <v>4.7389999999999999</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.188999999999993</v>
+        <v>66.119</v>
       </c>
       <c r="C51">
-        <v>4.3159999999999998</v>
+        <v>4.3230000000000004</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>66.03</v>
+        <v>65.959999999999994</v>
       </c>
       <c r="C52">
-        <v>3.464</v>
+        <v>3.472</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.881</v>
+        <v>65.811000000000007</v>
       </c>
       <c r="C53">
-        <v>3.0819999999999999</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.692999999999998</v>
+        <v>65.623000000000005</v>
       </c>
       <c r="C54">
-        <v>3.036</v>
+        <v>3.0449999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.498999999999995</v>
+        <v>65.429000000000002</v>
       </c>
       <c r="C55">
-        <v>3.1539999999999999</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>65.332999999999998</v>
+        <v>65.263000000000005</v>
       </c>
       <c r="C56" s="2">
-        <v>3.391</v>
+        <v>3.3959999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1384,6 +1384,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1678,15 +1687,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1721,6 +1721,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1739,14 +1747,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83C0C6E3-2C11-4C5B-AB77-97C6B55BC32B}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF04474-00BE-4BD3-9FBA-09785F09CCEF}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
         <v>60.26</v>
       </c>
       <c r="C2">
-        <v>7.7126000000000001</v>
+        <v>4.6870000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -470,7 +470,7 @@
         <v>64.522999999999996</v>
       </c>
       <c r="C3">
-        <v>3.8382000000000001</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -481,7 +481,7 @@
         <v>90.997</v>
       </c>
       <c r="C4">
-        <v>3.0581999999999998</v>
+        <v>2.9689999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>98.06</v>
       </c>
       <c r="C5">
-        <v>2.7736999999999998</v>
+        <v>3.0950000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -503,7 +503,7 @@
         <v>98.513999999999996</v>
       </c>
       <c r="C6">
-        <v>2.8881999999999999</v>
+        <v>2.5590000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -514,7 +514,7 @@
         <v>81.790000000000006</v>
       </c>
       <c r="C7">
-        <v>3.1429999999999998</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -525,7 +525,7 @@
         <v>79.22</v>
       </c>
       <c r="C8">
-        <v>2.9386999999999999</v>
+        <v>3.2309999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -533,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>83.408000000000001</v>
+        <v>82.822000000000003</v>
       </c>
       <c r="C9">
-        <v>2.8558500000000002</v>
+        <v>2.7250000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>86.516999999999996</v>
+        <v>84.521000000000001</v>
       </c>
       <c r="C10">
-        <v>2.7730000000000001</v>
+        <v>2.782</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>84.382000000000005</v>
+        <v>82.587000000000003</v>
       </c>
       <c r="C11">
-        <v>2.8109999999999999</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>82.528000000000006</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="C12">
-        <v>2.9740000000000002</v>
+        <v>3.0030000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>80.515000000000001</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="C13">
-        <v>3.4969999999999999</v>
+        <v>3.5190000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>78.853999999999999</v>
+        <v>77.608999999999995</v>
       </c>
       <c r="C14">
-        <v>3.8959999999999999</v>
+        <v>3.9249999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>77.73</v>
+        <v>76.605000000000004</v>
       </c>
       <c r="C15">
-        <v>3.5670000000000002</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>76.581999999999994</v>
+        <v>75.573999999999998</v>
       </c>
       <c r="C16">
-        <v>2.8959999999999999</v>
+        <v>2.9220000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>75.644000000000005</v>
+        <v>74.722999999999999</v>
       </c>
       <c r="C17">
-        <v>2.7679999999999998</v>
+        <v>2.7890000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.965000000000003</v>
+        <v>74.11</v>
       </c>
       <c r="C18">
-        <v>2.7850000000000001</v>
+        <v>2.8029999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>74.343999999999994</v>
+        <v>73.539000000000001</v>
       </c>
       <c r="C19">
-        <v>2.9260000000000002</v>
+        <v>2.944</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>73.736000000000004</v>
+        <v>72.984999999999999</v>
       </c>
       <c r="C20">
-        <v>3.1309999999999998</v>
+        <v>3.1520000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>73.277000000000001</v>
+        <v>72.563000000000002</v>
       </c>
       <c r="C21">
-        <v>3.2</v>
+        <v>3.2210000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.84</v>
+        <v>72.150000000000006</v>
       </c>
       <c r="C22">
-        <v>3.1859999999999999</v>
+        <v>3.2069999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.462999999999994</v>
+        <v>71.807000000000002</v>
       </c>
       <c r="C23">
-        <v>3.2669999999999999</v>
+        <v>3.2869999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>72.126999999999995</v>
+        <v>71.506</v>
       </c>
       <c r="C24">
-        <v>3.54</v>
+        <v>3.5569999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.745999999999995</v>
+        <v>71.150000000000006</v>
       </c>
       <c r="C25">
-        <v>4.1909999999999998</v>
+        <v>4.2080000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.418000000000006</v>
+        <v>70.831999999999994</v>
       </c>
       <c r="C26">
-        <v>4.6379999999999999</v>
+        <v>4.6550000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>71.135000000000005</v>
+        <v>70.558000000000007</v>
       </c>
       <c r="C27">
-        <v>4.2</v>
+        <v>4.2140000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.822999999999993</v>
+        <v>70.253</v>
       </c>
       <c r="C28">
-        <v>3.43</v>
+        <v>3.4449999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.581000000000003</v>
+        <v>70.021000000000001</v>
       </c>
       <c r="C29">
-        <v>3.18</v>
+        <v>3.1890000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.338999999999999</v>
+        <v>69.805000000000007</v>
       </c>
       <c r="C30">
-        <v>3.173</v>
+        <v>3.177</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.055000000000007</v>
+        <v>69.534999999999997</v>
       </c>
       <c r="C31">
-        <v>3.3159999999999998</v>
+        <v>3.3170000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.819999999999993</v>
+        <v>69.31</v>
       </c>
       <c r="C32">
-        <v>3.512</v>
+        <v>3.5150000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.602999999999994</v>
+        <v>69.122</v>
       </c>
       <c r="C33">
-        <v>3.5750000000000002</v>
+        <v>3.5790000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.384</v>
+        <v>68.927000000000007</v>
       </c>
       <c r="C34">
-        <v>3.5489999999999999</v>
+        <v>3.5550000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.203000000000003</v>
+        <v>68.756</v>
       </c>
       <c r="C35">
-        <v>3.601</v>
+        <v>3.6070000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.003</v>
+        <v>68.569999999999993</v>
       </c>
       <c r="C36">
-        <v>3.7650000000000001</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.772999999999996</v>
+        <v>68.356999999999999</v>
       </c>
       <c r="C37">
-        <v>4.3559999999999999</v>
+        <v>4.3620000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.56</v>
+        <v>68.156999999999996</v>
       </c>
       <c r="C38">
-        <v>4.7809999999999997</v>
+        <v>4.7880000000000003</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.36</v>
+        <v>67.97</v>
       </c>
       <c r="C39">
-        <v>4.3440000000000003</v>
+        <v>4.3529999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.167000000000002</v>
+        <v>67.787000000000006</v>
       </c>
       <c r="C40">
-        <v>3.4620000000000002</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.989000000000004</v>
+        <v>67.634</v>
       </c>
       <c r="C41">
-        <v>3.165</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.805000000000007</v>
+        <v>67.468000000000004</v>
       </c>
       <c r="C42">
-        <v>3.1469999999999998</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.593999999999994</v>
+        <v>67.266999999999996</v>
       </c>
       <c r="C43">
-        <v>3.2679999999999998</v>
+        <v>3.2719999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.406999999999996</v>
+        <v>67.087000000000003</v>
       </c>
       <c r="C44">
-        <v>3.468</v>
+        <v>3.472</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.221000000000004</v>
+        <v>66.900999999999996</v>
       </c>
       <c r="C45">
-        <v>3.5350000000000001</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.058999999999997</v>
+        <v>66.748999999999995</v>
       </c>
       <c r="C46">
-        <v>3.5190000000000001</v>
+        <v>3.5230000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.894999999999996</v>
+        <v>66.62</v>
       </c>
       <c r="C47">
-        <v>3.577</v>
+        <v>3.581</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.686000000000007</v>
+        <v>66.457999999999998</v>
       </c>
       <c r="C48">
-        <v>3.734</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.477000000000004</v>
+        <v>66.266999999999996</v>
       </c>
       <c r="C49">
-        <v>4.3079999999999998</v>
+        <v>4.3150000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.283000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="C50">
-        <v>4.75</v>
+        <v>4.7590000000000003</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.119</v>
+        <v>65.936000000000007</v>
       </c>
       <c r="C51">
-        <v>4.3230000000000004</v>
+        <v>4.3330000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.959999999999994</v>
+        <v>65.793000000000006</v>
       </c>
       <c r="C52">
-        <v>3.472</v>
+        <v>3.4860000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.811000000000007</v>
+        <v>65.653999999999996</v>
       </c>
       <c r="C53">
-        <v>3.09</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.623000000000005</v>
+        <v>65.483000000000004</v>
       </c>
       <c r="C54">
-        <v>3.0449999999999999</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.429000000000002</v>
+        <v>65.308999999999997</v>
       </c>
       <c r="C55">
-        <v>3.1589999999999998</v>
+        <v>3.1749999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>65.263000000000005</v>
+        <v>65.146000000000001</v>
       </c>
       <c r="C56" s="2">
-        <v>3.3959999999999999</v>
+        <v>3.4129999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47696</v>
       </c>
       <c r="B57" s="2">
-        <v>64.263000000000005</v>
+        <v>64.971999999999994</v>
       </c>
       <c r="C57" s="2">
-        <v>3.4769999999999999</v>
+        <v>3.4590000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47727</v>
       </c>
       <c r="B58" s="2">
-        <v>64.150000000000006</v>
+        <v>64.846000000000004</v>
       </c>
       <c r="C58" s="2">
-        <v>3.4449999999999998</v>
+        <v>3.4350000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47757</v>
       </c>
       <c r="B59" s="2">
-        <v>64.040000000000006</v>
+        <v>64.738</v>
       </c>
       <c r="C59" s="2">
-        <v>3.5230000000000001</v>
+        <v>3.5110000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>47788</v>
       </c>
       <c r="B60" s="2">
-        <v>63.896000000000001</v>
+        <v>64.557000000000002</v>
       </c>
       <c r="C60" s="2">
-        <v>3.6909999999999998</v>
+        <v>3.669</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1105,10 +1105,10 @@
         <v>47818</v>
       </c>
       <c r="B61" s="2">
-        <v>63.716999999999999</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="C61" s="2">
-        <v>4.226</v>
+        <v>4.218</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1116,10 +1116,10 @@
         <v>47849</v>
       </c>
       <c r="B62" s="2">
-        <v>63.564</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="C62" s="2">
-        <v>4.6340000000000003</v>
+        <v>4.6390000000000002</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1127,10 +1127,10 @@
         <v>47880</v>
       </c>
       <c r="B63" s="2">
-        <v>63.451999999999998</v>
+        <v>64.064999999999998</v>
       </c>
       <c r="C63" s="2">
-        <v>4.22</v>
+        <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,10 +1138,10 @@
         <v>47908</v>
       </c>
       <c r="B64" s="2">
-        <v>63.326999999999998</v>
+        <v>63.927</v>
       </c>
       <c r="C64" s="2">
-        <v>3.46</v>
+        <v>3.4340000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1149,10 +1149,10 @@
         <v>47939</v>
       </c>
       <c r="B65" s="2">
-        <v>63.203000000000003</v>
+        <v>63.762999999999998</v>
       </c>
       <c r="C65" s="2">
-        <v>3.0870000000000002</v>
+        <v>3.0590000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1160,10 +1160,10 @@
         <v>47969</v>
       </c>
       <c r="B66" s="2">
-        <v>63.057000000000002</v>
+        <v>63.613</v>
       </c>
       <c r="C66" s="2">
-        <v>3.0510000000000002</v>
+        <v>3.0209999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1171,10 +1171,10 @@
         <v>48000</v>
       </c>
       <c r="B67" s="2">
-        <v>62.914000000000001</v>
+        <v>63.454999999999998</v>
       </c>
       <c r="C67" s="2">
-        <v>3.1720000000000002</v>
+        <v>3.1429999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1182,10 +1182,10 @@
         <v>48030</v>
       </c>
       <c r="B68" s="2">
-        <v>62.789000000000001</v>
+        <v>63.302</v>
       </c>
       <c r="C68" s="2">
-        <v>3.3740000000000001</v>
+        <v>3.3530000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>48061</v>
       </c>
       <c r="B69" s="2">
-        <v>62.656999999999996</v>
+        <v>63.156999999999996</v>
       </c>
       <c r="C69" s="2">
-        <v>3.4289999999999998</v>
+        <v>3.415</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1204,10 +1204,10 @@
         <v>48092</v>
       </c>
       <c r="B70" s="2">
-        <v>62.536000000000001</v>
+        <v>63.024000000000001</v>
       </c>
       <c r="C70" s="2">
-        <v>3.4129999999999998</v>
+        <v>3.3980000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,10 +1215,10 @@
         <v>48122</v>
       </c>
       <c r="B71" s="2">
-        <v>62.405000000000001</v>
+        <v>62.857999999999997</v>
       </c>
       <c r="C71" s="2">
-        <v>3.4950000000000001</v>
+        <v>3.4830000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1226,10 +1226,10 @@
         <v>48153</v>
       </c>
       <c r="B72" s="2">
-        <v>62.277999999999999</v>
+        <v>62.704999999999998</v>
       </c>
       <c r="C72" s="2">
-        <v>3.7309999999999999</v>
+        <v>3.7120000000000002</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>48183</v>
       </c>
       <c r="B73" s="2">
-        <v>62.119</v>
+        <v>62.509</v>
       </c>
       <c r="C73" s="2">
-        <v>4.3259999999999996</v>
+        <v>4.3150000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1248,10 +1248,10 @@
         <v>48214</v>
       </c>
       <c r="B74" s="2">
-        <v>61.978000000000002</v>
+        <v>62.372</v>
       </c>
       <c r="C74" s="2">
-        <v>4.665</v>
+        <v>4.6520000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1259,10 +1259,10 @@
         <v>48245</v>
       </c>
       <c r="B75" s="2">
-        <v>61.871000000000002</v>
+        <v>62.258000000000003</v>
       </c>
       <c r="C75" s="2">
-        <v>4.24</v>
+        <v>4.2439999999999998</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1270,10 +1270,10 @@
         <v>48274</v>
       </c>
       <c r="B76" s="2">
-        <v>61.749000000000002</v>
+        <v>62.094000000000001</v>
       </c>
       <c r="C76" s="2">
-        <v>3.4239999999999999</v>
+        <v>3.3980000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1281,10 +1281,10 @@
         <v>48305</v>
       </c>
       <c r="B77" s="2">
-        <v>61.595999999999997</v>
+        <v>61.914999999999999</v>
       </c>
       <c r="C77" s="2">
-        <v>2.9820000000000002</v>
+        <v>2.9649999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1292,10 +1292,10 @@
         <v>48335</v>
       </c>
       <c r="B78" s="2">
-        <v>61.472000000000001</v>
+        <v>61.768999999999998</v>
       </c>
       <c r="C78" s="2">
-        <v>2.952</v>
+        <v>2.9329999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1303,10 +1303,10 @@
         <v>48366</v>
       </c>
       <c r="B79" s="2">
-        <v>61.32</v>
+        <v>61.600999999999999</v>
       </c>
       <c r="C79" s="2">
-        <v>3.0870000000000002</v>
+        <v>3.0470000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1314,10 +1314,10 @@
         <v>48396</v>
       </c>
       <c r="B80" s="2">
-        <v>61.151000000000003</v>
+        <v>61.411000000000001</v>
       </c>
       <c r="C80" s="2">
-        <v>3.266</v>
+        <v>3.2280000000000002</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1325,10 +1325,10 @@
         <v>48427</v>
       </c>
       <c r="B81" s="2">
-        <v>61.002000000000002</v>
+        <v>61.265000000000001</v>
       </c>
       <c r="C81" s="2">
-        <v>3.319</v>
+        <v>3.2789999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1336,10 +1336,10 @@
         <v>48458</v>
       </c>
       <c r="B82" s="2">
-        <v>60.88</v>
+        <v>61.143000000000001</v>
       </c>
       <c r="C82" s="2">
-        <v>3.294</v>
+        <v>3.2559999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1347,10 +1347,10 @@
         <v>48488</v>
       </c>
       <c r="B83" s="2">
-        <v>60.76</v>
+        <v>61.006999999999998</v>
       </c>
       <c r="C83" s="2">
-        <v>3.359</v>
+        <v>3.3220000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1358,10 +1358,10 @@
         <v>48519</v>
       </c>
       <c r="B84" s="2">
-        <v>60.64</v>
+        <v>60.874000000000002</v>
       </c>
       <c r="C84" s="2">
-        <v>3.5739999999999998</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,30 +1369,21 @@
         <v>48549</v>
       </c>
       <c r="B85" s="2">
-        <v>60.506999999999998</v>
+        <v>60.713000000000001</v>
       </c>
       <c r="C85" s="2">
-        <v>4.093</v>
+        <v>4.0670000000000002</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A57:B85 A2:A55 A56" numberStoredAsText="1"/>
+    <ignoredError sqref="A57:A85 A2:A55 A56" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1687,6 +1678,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1721,14 +1721,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1747,6 +1739,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF04474-00BE-4BD3-9FBA-09785F09CCEF}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BE488C-1B51-4047-BBAE-41C440E938E3}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
@@ -533,7 +533,7 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.822000000000003</v>
+        <v>82.191000000000003</v>
       </c>
       <c r="C9">
         <v>2.7250000000000001</v>
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>84.521000000000001</v>
+        <v>81.936999999999998</v>
       </c>
       <c r="C10">
-        <v>2.782</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>82.587000000000003</v>
+        <v>80.251000000000005</v>
       </c>
       <c r="C11">
-        <v>2.835</v>
+        <v>2.8210000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>80.900000000000006</v>
+        <v>78.77</v>
       </c>
       <c r="C12">
-        <v>3.0030000000000001</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>79.099999999999994</v>
+        <v>77.222999999999999</v>
       </c>
       <c r="C13">
-        <v>3.5190000000000001</v>
+        <v>3.5059999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>77.608999999999995</v>
+        <v>75.959000000000003</v>
       </c>
       <c r="C14">
-        <v>3.9249999999999998</v>
+        <v>3.9089999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>76.605000000000004</v>
+        <v>75.106999999999999</v>
       </c>
       <c r="C15">
-        <v>3.593</v>
+        <v>3.5750000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>75.573999999999998</v>
+        <v>74.228999999999999</v>
       </c>
       <c r="C16">
-        <v>2.9220000000000002</v>
+        <v>2.9129999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>74.722999999999999</v>
+        <v>73.504999999999995</v>
       </c>
       <c r="C17">
-        <v>2.7890000000000001</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.11</v>
+        <v>72.977000000000004</v>
       </c>
       <c r="C18">
-        <v>2.8029999999999999</v>
+        <v>2.7949999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>73.539000000000001</v>
+        <v>72.489000000000004</v>
       </c>
       <c r="C19">
-        <v>2.944</v>
+        <v>2.9380000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>72.984999999999999</v>
+        <v>72.007999999999996</v>
       </c>
       <c r="C20">
-        <v>3.1520000000000001</v>
+        <v>3.1469999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>72.563000000000002</v>
+        <v>71.644999999999996</v>
       </c>
       <c r="C21">
-        <v>3.2210000000000001</v>
+        <v>3.2160000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.150000000000006</v>
+        <v>71.296999999999997</v>
       </c>
       <c r="C22">
-        <v>3.2069999999999999</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>71.807000000000002</v>
+        <v>71</v>
       </c>
       <c r="C23">
-        <v>3.2869999999999999</v>
+        <v>3.2810000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>71.506</v>
+        <v>70.736999999999995</v>
       </c>
       <c r="C24">
-        <v>3.5569999999999999</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.150000000000006</v>
+        <v>70.427999999999997</v>
       </c>
       <c r="C25">
-        <v>4.2080000000000002</v>
+        <v>4.1980000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>70.831999999999994</v>
+        <v>70.156000000000006</v>
       </c>
       <c r="C26">
-        <v>4.6550000000000002</v>
+        <v>4.6479999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.558000000000007</v>
+        <v>69.92</v>
       </c>
       <c r="C27">
-        <v>4.2140000000000004</v>
+        <v>4.2069999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.253</v>
+        <v>69.667000000000002</v>
       </c>
       <c r="C28">
-        <v>3.4449999999999998</v>
+        <v>3.4390000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.021000000000001</v>
+        <v>69.466999999999999</v>
       </c>
       <c r="C29">
-        <v>3.1890000000000001</v>
+        <v>3.181</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>69.805000000000007</v>
+        <v>69.27</v>
       </c>
       <c r="C30">
-        <v>3.177</v>
+        <v>3.1680000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.534999999999997</v>
+        <v>69.022000000000006</v>
       </c>
       <c r="C31">
-        <v>3.3170000000000002</v>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.31</v>
+        <v>68.816999999999993</v>
       </c>
       <c r="C32">
-        <v>3.5150000000000001</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.122</v>
+        <v>68.644999999999996</v>
       </c>
       <c r="C33">
-        <v>3.5790000000000002</v>
+        <v>3.573</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.927000000000007</v>
+        <v>68.463999999999999</v>
       </c>
       <c r="C34">
-        <v>3.5550000000000002</v>
+        <v>3.5489999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.756</v>
+        <v>68.308999999999997</v>
       </c>
       <c r="C35">
-        <v>3.6070000000000002</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.569999999999993</v>
+        <v>68.132999999999996</v>
       </c>
       <c r="C36">
-        <v>3.77</v>
+        <v>3.7610000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.356999999999999</v>
+        <v>67.933999999999997</v>
       </c>
       <c r="C37">
-        <v>4.3620000000000001</v>
+        <v>4.3479999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.156999999999996</v>
+        <v>67.753</v>
       </c>
       <c r="C38">
-        <v>4.7880000000000003</v>
+        <v>4.7679999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.97</v>
+        <v>67.588999999999999</v>
       </c>
       <c r="C39">
-        <v>4.3529999999999998</v>
+        <v>4.3319999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.787000000000006</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="C40">
-        <v>3.468</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.634</v>
+        <v>67.287000000000006</v>
       </c>
       <c r="C41">
-        <v>3.169</v>
+        <v>3.1539999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.468000000000004</v>
+        <v>67.131</v>
       </c>
       <c r="C42">
-        <v>3.15</v>
+        <v>3.1349999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.266999999999996</v>
+        <v>66.941000000000003</v>
       </c>
       <c r="C43">
-        <v>3.2719999999999998</v>
+        <v>3.2559999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.087000000000003</v>
+        <v>66.777000000000001</v>
       </c>
       <c r="C44">
-        <v>3.472</v>
+        <v>3.4590000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.900999999999996</v>
+        <v>66.617999999999995</v>
       </c>
       <c r="C45">
-        <v>3.5390000000000001</v>
+        <v>3.5259999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.748999999999995</v>
+        <v>66.478999999999999</v>
       </c>
       <c r="C46">
-        <v>3.5230000000000001</v>
+        <v>3.5110000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.62</v>
+        <v>66.352999999999994</v>
       </c>
       <c r="C47">
-        <v>3.581</v>
+        <v>3.569</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.457999999999998</v>
+        <v>66.200999999999993</v>
       </c>
       <c r="C48">
-        <v>3.74</v>
+        <v>3.7280000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.266999999999996</v>
+        <v>66.024000000000001</v>
       </c>
       <c r="C49">
-        <v>4.3150000000000004</v>
+        <v>4.3029999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.08</v>
+        <v>65.852999999999994</v>
       </c>
       <c r="C50">
-        <v>4.7590000000000003</v>
+        <v>4.7469999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.936000000000007</v>
+        <v>65.718999999999994</v>
       </c>
       <c r="C51">
-        <v>4.3330000000000002</v>
+        <v>4.3170000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.793000000000006</v>
+        <v>65.59</v>
       </c>
       <c r="C52">
-        <v>3.4860000000000002</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.653999999999996</v>
+        <v>65.463999999999999</v>
       </c>
       <c r="C53">
-        <v>3.105</v>
+        <v>3.0870000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.483000000000004</v>
+        <v>65.293000000000006</v>
       </c>
       <c r="C54">
-        <v>3.06</v>
+        <v>3.0419999999999998</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.308999999999997</v>
+        <v>65.129000000000005</v>
       </c>
       <c r="C55">
-        <v>3.1749999999999998</v>
+        <v>3.1579999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>65.146000000000001</v>
+        <v>64.986000000000004</v>
       </c>
       <c r="C56" s="2">
-        <v>3.4129999999999998</v>
+        <v>3.3959999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47696</v>
       </c>
       <c r="B57" s="2">
-        <v>64.971999999999994</v>
+        <v>64.814999999999998</v>
       </c>
       <c r="C57" s="2">
-        <v>3.4590000000000001</v>
+        <v>3.444</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47727</v>
       </c>
       <c r="B58" s="2">
-        <v>64.846000000000004</v>
+        <v>64.698999999999998</v>
       </c>
       <c r="C58" s="2">
-        <v>3.4350000000000001</v>
+        <v>3.4209999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47757</v>
       </c>
       <c r="B59" s="2">
-        <v>64.738</v>
+        <v>64.600999999999999</v>
       </c>
       <c r="C59" s="2">
-        <v>3.5110000000000001</v>
+        <v>3.4969999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>47788</v>
       </c>
       <c r="B60" s="2">
-        <v>64.557000000000002</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="C60" s="2">
-        <v>3.669</v>
+        <v>3.6549999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1105,10 +1105,10 @@
         <v>47818</v>
       </c>
       <c r="B61" s="2">
-        <v>64.349999999999994</v>
+        <v>64.233000000000004</v>
       </c>
       <c r="C61" s="2">
-        <v>4.218</v>
+        <v>4.2039999999999997</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1116,10 +1116,10 @@
         <v>47849</v>
       </c>
       <c r="B62" s="2">
-        <v>64.180000000000007</v>
+        <v>64.069999999999993</v>
       </c>
       <c r="C62" s="2">
-        <v>4.6390000000000002</v>
+        <v>4.625</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1127,10 +1127,10 @@
         <v>47880</v>
       </c>
       <c r="B63" s="2">
-        <v>64.064999999999998</v>
+        <v>63.954999999999998</v>
       </c>
       <c r="C63" s="2">
-        <v>4.2300000000000004</v>
+        <v>4.2160000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,10 +1138,10 @@
         <v>47908</v>
       </c>
       <c r="B64" s="2">
-        <v>63.927</v>
+        <v>63.823</v>
       </c>
       <c r="C64" s="2">
-        <v>3.4340000000000002</v>
+        <v>3.4260000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1149,10 +1149,10 @@
         <v>47939</v>
       </c>
       <c r="B65" s="2">
-        <v>63.762999999999998</v>
+        <v>63.676000000000002</v>
       </c>
       <c r="C65" s="2">
-        <v>3.0590000000000002</v>
+        <v>3.052</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1160,10 +1160,10 @@
         <v>47969</v>
       </c>
       <c r="B66" s="2">
-        <v>63.613</v>
+        <v>63.536999999999999</v>
       </c>
       <c r="C66" s="2">
-        <v>3.0209999999999999</v>
+        <v>3.0139999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1171,10 +1171,10 @@
         <v>48000</v>
       </c>
       <c r="B67" s="2">
-        <v>63.454999999999998</v>
+        <v>63.387999999999998</v>
       </c>
       <c r="C67" s="2">
-        <v>3.1429999999999998</v>
+        <v>3.1360000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1182,10 +1182,10 @@
         <v>48030</v>
       </c>
       <c r="B68" s="2">
-        <v>63.302</v>
+        <v>63.244999999999997</v>
       </c>
       <c r="C68" s="2">
-        <v>3.3530000000000002</v>
+        <v>3.3559999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>48061</v>
       </c>
       <c r="B69" s="2">
-        <v>63.156999999999996</v>
+        <v>63.11</v>
       </c>
       <c r="C69" s="2">
-        <v>3.415</v>
+        <v>3.4180000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1204,10 +1204,10 @@
         <v>48092</v>
       </c>
       <c r="B70" s="2">
-        <v>63.024000000000001</v>
+        <v>62.99</v>
       </c>
       <c r="C70" s="2">
-        <v>3.3980000000000001</v>
+        <v>3.4009999999999998</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,10 +1215,10 @@
         <v>48122</v>
       </c>
       <c r="B71" s="2">
-        <v>62.857999999999997</v>
+        <v>62.841000000000001</v>
       </c>
       <c r="C71" s="2">
-        <v>3.4830000000000001</v>
+        <v>3.4860000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1226,10 +1226,10 @@
         <v>48153</v>
       </c>
       <c r="B72" s="2">
-        <v>62.704999999999998</v>
+        <v>62.697000000000003</v>
       </c>
       <c r="C72" s="2">
-        <v>3.7120000000000002</v>
+        <v>3.7149999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>48183</v>
       </c>
       <c r="B73" s="2">
-        <v>62.509</v>
+        <v>62.512</v>
       </c>
       <c r="C73" s="2">
-        <v>4.3150000000000004</v>
+        <v>4.3179999999999996</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1248,10 +1248,10 @@
         <v>48214</v>
       </c>
       <c r="B74" s="2">
-        <v>62.372</v>
+        <v>62.381999999999998</v>
       </c>
       <c r="C74" s="2">
-        <v>4.6520000000000001</v>
+        <v>4.6550000000000002</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1259,10 +1259,10 @@
         <v>48245</v>
       </c>
       <c r="B75" s="2">
-        <v>62.258000000000003</v>
+        <v>62.271000000000001</v>
       </c>
       <c r="C75" s="2">
-        <v>4.2439999999999998</v>
+        <v>4.2469999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1270,10 +1270,10 @@
         <v>48274</v>
       </c>
       <c r="B76" s="2">
-        <v>62.094000000000001</v>
+        <v>62.116</v>
       </c>
       <c r="C76" s="2">
-        <v>3.3980000000000001</v>
+        <v>3.4009999999999998</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1281,10 +1281,10 @@
         <v>48305</v>
       </c>
       <c r="B77" s="2">
-        <v>61.914999999999999</v>
+        <v>61.948999999999998</v>
       </c>
       <c r="C77" s="2">
-        <v>2.9649999999999999</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1292,10 +1292,10 @@
         <v>48335</v>
       </c>
       <c r="B78" s="2">
-        <v>61.768999999999998</v>
+        <v>61.808999999999997</v>
       </c>
       <c r="C78" s="2">
-        <v>2.9329999999999998</v>
+        <v>2.9359999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1303,10 +1303,10 @@
         <v>48366</v>
       </c>
       <c r="B79" s="2">
-        <v>61.600999999999999</v>
+        <v>61.643999999999998</v>
       </c>
       <c r="C79" s="2">
-        <v>3.0470000000000002</v>
+        <v>3.0510000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1314,10 +1314,10 @@
         <v>48396</v>
       </c>
       <c r="B80" s="2">
-        <v>61.411000000000001</v>
+        <v>61.465000000000003</v>
       </c>
       <c r="C80" s="2">
-        <v>3.2280000000000002</v>
+        <v>3.2320000000000002</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1325,10 +1325,10 @@
         <v>48427</v>
       </c>
       <c r="B81" s="2">
-        <v>61.265000000000001</v>
+        <v>61.328000000000003</v>
       </c>
       <c r="C81" s="2">
-        <v>3.2789999999999999</v>
+        <v>3.2839999999999998</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1336,10 +1336,10 @@
         <v>48458</v>
       </c>
       <c r="B82" s="2">
-        <v>61.143000000000001</v>
+        <v>61.213000000000001</v>
       </c>
       <c r="C82" s="2">
-        <v>3.2559999999999998</v>
+        <v>3.2589999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1347,10 +1347,10 @@
         <v>48488</v>
       </c>
       <c r="B83" s="2">
-        <v>61.006999999999998</v>
+        <v>61.08</v>
       </c>
       <c r="C83" s="2">
-        <v>3.3220000000000001</v>
+        <v>3.3239999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1358,10 +1358,10 @@
         <v>48519</v>
       </c>
       <c r="B84" s="2">
-        <v>60.874000000000002</v>
+        <v>60.954000000000001</v>
       </c>
       <c r="C84" s="2">
-        <v>3.5369999999999999</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,10 +1369,15 @@
         <v>48549</v>
       </c>
       <c r="B85" s="2">
-        <v>60.713000000000001</v>
+        <v>60.792999999999999</v>
       </c>
       <c r="C85" s="2">
-        <v>4.0670000000000002</v>
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <v>4.3899999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1384,6 +1389,48 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1678,49 +1725,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1737,23 +1761,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BE488C-1B51-4047-BBAE-41C440E938E3}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1548BE3-4334-4867-B8AB-E30CE848106E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
@@ -1375,11 +1375,6 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C86">
-        <v>4.3899999999999997</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -1389,6 +1384,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
@@ -1419,15 +1423,6 @@
     </_ApprovalSentBy>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1726,20 +1721,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
     <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1548BE3-4334-4867-B8AB-E30CE848106E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79258330-8898-4A61-8C72-0B78F5941B0E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
         <v>98.513999999999996</v>
       </c>
       <c r="C6">
-        <v>2.5590000000000002</v>
+        <v>2.8881999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -514,7 +514,7 @@
         <v>81.790000000000006</v>
       </c>
       <c r="C7">
-        <v>3.04</v>
+        <v>3.1429999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -525,7 +525,7 @@
         <v>79.22</v>
       </c>
       <c r="C8">
-        <v>3.2309999999999999</v>
+        <v>2.9386999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -533,10 +533,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.191000000000003</v>
+        <v>82.352000000000004</v>
       </c>
       <c r="C9">
-        <v>2.7250000000000001</v>
+        <v>2.9228499999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +544,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>81.936999999999998</v>
+        <v>83.084000000000003</v>
       </c>
       <c r="C10">
-        <v>2.77</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>80.251000000000005</v>
+        <v>81.293999999999997</v>
       </c>
       <c r="C11">
-        <v>2.8210000000000002</v>
+        <v>2.9140000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>78.77</v>
+        <v>79.665000000000006</v>
       </c>
       <c r="C12">
-        <v>2.988</v>
+        <v>3.0710000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>77.222999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="C13">
-        <v>3.5059999999999998</v>
+        <v>3.581</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>75.959000000000003</v>
+        <v>76.296000000000006</v>
       </c>
       <c r="C14">
-        <v>3.9089999999999998</v>
+        <v>3.9790000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>75.106999999999999</v>
+        <v>75.284999999999997</v>
       </c>
       <c r="C15">
-        <v>3.5750000000000002</v>
+        <v>3.6379999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>74.228999999999999</v>
+        <v>74.256</v>
       </c>
       <c r="C16">
-        <v>2.9129999999999998</v>
+        <v>2.9489999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.504999999999995</v>
+        <v>73.415999999999997</v>
       </c>
       <c r="C17">
-        <v>2.78</v>
+        <v>2.8130000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.977000000000004</v>
+        <v>72.816000000000003</v>
       </c>
       <c r="C18">
-        <v>2.7949999999999999</v>
+        <v>2.8239999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.489000000000004</v>
+        <v>72.266999999999996</v>
       </c>
       <c r="C19">
-        <v>2.9380000000000002</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>72.007999999999996</v>
+        <v>71.75</v>
       </c>
       <c r="C20">
-        <v>3.1469999999999998</v>
+        <v>3.1709999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.644999999999996</v>
+        <v>71.366</v>
       </c>
       <c r="C21">
-        <v>3.2160000000000002</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>71.296999999999997</v>
+        <v>70.989999999999995</v>
       </c>
       <c r="C22">
-        <v>3.202</v>
+        <v>3.2269999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>70.673000000000002</v>
       </c>
       <c r="C23">
-        <v>3.2810000000000001</v>
+        <v>3.3090000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.736999999999995</v>
+        <v>70.391000000000005</v>
       </c>
       <c r="C24">
-        <v>3.5489999999999999</v>
+        <v>3.5720000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.427999999999997</v>
+        <v>70.061000000000007</v>
       </c>
       <c r="C25">
-        <v>4.1980000000000004</v>
+        <v>4.2039999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>70.156000000000006</v>
+        <v>69.775999999999996</v>
       </c>
       <c r="C26">
-        <v>4.6479999999999997</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.92</v>
+        <v>69.537999999999997</v>
       </c>
       <c r="C27">
-        <v>4.2069999999999999</v>
+        <v>4.2140000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.667000000000002</v>
+        <v>69.277000000000001</v>
       </c>
       <c r="C28">
-        <v>3.4390000000000001</v>
+        <v>3.4510000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.466999999999999</v>
+        <v>69.082999999999998</v>
       </c>
       <c r="C29">
-        <v>3.181</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>69.27</v>
+        <v>68.903000000000006</v>
       </c>
       <c r="C30">
-        <v>3.1680000000000001</v>
+        <v>3.1890000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.022000000000006</v>
+        <v>68.67</v>
       </c>
       <c r="C31">
-        <v>3.3109999999999999</v>
+        <v>3.3370000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.816999999999993</v>
+        <v>68.477000000000004</v>
       </c>
       <c r="C32">
-        <v>3.51</v>
+        <v>3.5379999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.644999999999996</v>
+        <v>68.308000000000007</v>
       </c>
       <c r="C33">
-        <v>3.573</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.463999999999999</v>
+        <v>68.138000000000005</v>
       </c>
       <c r="C34">
-        <v>3.5489999999999999</v>
+        <v>3.577</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.308999999999997</v>
+        <v>67.998999999999995</v>
       </c>
       <c r="C35">
-        <v>3.601</v>
+        <v>3.6269999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.132999999999996</v>
+        <v>67.852999999999994</v>
       </c>
       <c r="C36">
-        <v>3.7610000000000001</v>
+        <v>3.7810000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.933999999999997</v>
+        <v>67.677000000000007</v>
       </c>
       <c r="C37">
-        <v>4.3479999999999999</v>
+        <v>4.3680000000000003</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.753</v>
+        <v>67.503</v>
       </c>
       <c r="C38">
-        <v>4.7679999999999998</v>
+        <v>4.7880000000000003</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.588999999999999</v>
+        <v>67.343000000000004</v>
       </c>
       <c r="C39">
-        <v>4.3319999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.430000000000007</v>
+        <v>67.197000000000003</v>
       </c>
       <c r="C40">
-        <v>3.45</v>
+        <v>3.4670000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.287000000000006</v>
+        <v>67.069999999999993</v>
       </c>
       <c r="C41">
-        <v>3.1539999999999999</v>
+        <v>3.1789999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.131</v>
+        <v>66.926000000000002</v>
       </c>
       <c r="C42">
-        <v>3.1349999999999998</v>
+        <v>3.1640000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.941000000000003</v>
+        <v>66.751000000000005</v>
       </c>
       <c r="C43">
-        <v>3.2559999999999998</v>
+        <v>3.2869999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.777000000000001</v>
+        <v>66.59</v>
       </c>
       <c r="C44">
-        <v>3.4590000000000001</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.617999999999995</v>
+        <v>66.444999999999993</v>
       </c>
       <c r="C45">
-        <v>3.5259999999999998</v>
+        <v>3.5590000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.478999999999999</v>
+        <v>66.322000000000003</v>
       </c>
       <c r="C46">
-        <v>3.5110000000000001</v>
+        <v>3.544</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.352999999999994</v>
+        <v>66.2</v>
       </c>
       <c r="C47">
-        <v>3.569</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.200999999999993</v>
+        <v>66.045000000000002</v>
       </c>
       <c r="C48">
-        <v>3.7280000000000002</v>
+        <v>3.7570000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.024000000000001</v>
+        <v>65.876999999999995</v>
       </c>
       <c r="C49">
-        <v>4.3029999999999999</v>
+        <v>4.3289999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.852999999999994</v>
+        <v>65.716999999999999</v>
       </c>
       <c r="C50">
-        <v>4.7469999999999999</v>
+        <v>4.774</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.718999999999994</v>
+        <v>65.594999999999999</v>
       </c>
       <c r="C51">
-        <v>4.3170000000000002</v>
+        <v>4.3449999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.59</v>
+        <v>65.486999999999995</v>
       </c>
       <c r="C52">
-        <v>3.468</v>
+        <v>3.4969999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.463999999999999</v>
+        <v>65.376999999999995</v>
       </c>
       <c r="C53">
-        <v>3.0870000000000002</v>
+        <v>3.1179999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.293000000000006</v>
+        <v>65.215999999999994</v>
       </c>
       <c r="C54">
-        <v>3.0419999999999998</v>
+        <v>3.0760000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.129000000000005</v>
+        <v>65.061999999999998</v>
       </c>
       <c r="C55">
-        <v>3.1579999999999999</v>
+        <v>3.1890000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.986000000000004</v>
+        <v>64.929000000000002</v>
       </c>
       <c r="C56" s="2">
-        <v>3.3959999999999999</v>
+        <v>3.419</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1393,39 +1393,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1720,6 +1687,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
@@ -1729,17 +1729,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1756,4 +1745,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79258330-8898-4A61-8C72-0B78F5941B0E}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBDD28FD-DE88-4884-A202-035D994C2181}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
   <si>
     <t>oil_price</t>
   </si>
@@ -42,6 +43,33 @@
   </si>
   <si>
     <t>gas_price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>WTI</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>SourceWTI</t>
+  </si>
+  <si>
+    <t>SourceHH</t>
+  </si>
+  <si>
+    <t>MaxAsOfDate</t>
+  </si>
+  <si>
+    <t>SETTLED</t>
+  </si>
+  <si>
+    <t>STRIP</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -79,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -94,6 +122,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,10 +562,10 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.352000000000004</v>
+        <v>82.34</v>
       </c>
       <c r="C9">
-        <v>2.9228499999999999</v>
+        <v>2.9386999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,10 +573,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>83.084000000000003</v>
+        <v>82.950999999999993</v>
       </c>
       <c r="C10">
-        <v>2.907</v>
+        <v>2.9386999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,10 +584,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>81.293999999999997</v>
+        <v>81.165000000000006</v>
       </c>
       <c r="C11">
-        <v>2.9140000000000001</v>
+        <v>2.8879999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +595,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>79.665000000000006</v>
+        <v>79.572999999999993</v>
       </c>
       <c r="C12">
-        <v>3.0710000000000002</v>
+        <v>3.0350000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +606,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>77.83</v>
+        <v>77.81</v>
       </c>
       <c r="C13">
-        <v>3.581</v>
+        <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +617,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>76.296000000000006</v>
+        <v>76.319000000000003</v>
       </c>
       <c r="C14">
-        <v>3.9790000000000001</v>
+        <v>3.9369999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +628,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>75.284999999999997</v>
+        <v>75.319000000000003</v>
       </c>
       <c r="C15">
-        <v>3.6379999999999999</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +639,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>74.256</v>
+        <v>74.311999999999998</v>
       </c>
       <c r="C16">
-        <v>2.9489999999999998</v>
+        <v>2.9209999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +650,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.415999999999997</v>
+        <v>73.489999999999995</v>
       </c>
       <c r="C17">
-        <v>2.8130000000000002</v>
+        <v>2.786</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +661,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.816000000000003</v>
+        <v>72.899000000000001</v>
       </c>
       <c r="C18">
-        <v>2.8239999999999998</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +672,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.266999999999996</v>
+        <v>72.36</v>
       </c>
       <c r="C19">
-        <v>2.964</v>
+        <v>2.9420000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +683,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>71.75</v>
+        <v>71.846000000000004</v>
       </c>
       <c r="C20">
-        <v>3.1709999999999998</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +694,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.366</v>
+        <v>71.456000000000003</v>
       </c>
       <c r="C21">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +705,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>70.989999999999995</v>
+        <v>71.082999999999998</v>
       </c>
       <c r="C22">
-        <v>3.2269999999999999</v>
+        <v>3.206</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +716,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>70.673000000000002</v>
+        <v>70.766999999999996</v>
       </c>
       <c r="C23">
-        <v>3.3090000000000002</v>
+        <v>3.2869999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +727,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.391000000000005</v>
+        <v>70.468999999999994</v>
       </c>
       <c r="C24">
-        <v>3.5720000000000001</v>
+        <v>3.5459999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +738,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.061000000000007</v>
+        <v>70.131</v>
       </c>
       <c r="C25">
-        <v>4.2039999999999997</v>
+        <v>4.1749999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +749,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>69.775999999999996</v>
+        <v>69.846000000000004</v>
       </c>
       <c r="C26">
-        <v>4.6500000000000004</v>
+        <v>4.6210000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +760,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.537999999999997</v>
+        <v>69.61</v>
       </c>
       <c r="C27">
-        <v>4.2140000000000004</v>
+        <v>4.1829999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +771,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.277000000000001</v>
+        <v>69.356999999999999</v>
       </c>
       <c r="C28">
-        <v>3.4510000000000001</v>
+        <v>3.431</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +782,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.082999999999998</v>
+        <v>69.16</v>
       </c>
       <c r="C29">
-        <v>3.202</v>
+        <v>3.181</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +793,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>68.903000000000006</v>
+        <v>68.972999999999999</v>
       </c>
       <c r="C30">
-        <v>3.1890000000000001</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +804,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>68.67</v>
+        <v>68.739999999999995</v>
       </c>
       <c r="C31">
-        <v>3.3370000000000002</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +815,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.477000000000004</v>
+        <v>68.546999999999997</v>
       </c>
       <c r="C32">
-        <v>3.5379999999999998</v>
+        <v>3.5209999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +826,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.308000000000007</v>
+        <v>68.375</v>
       </c>
       <c r="C33">
-        <v>3.601</v>
+        <v>3.5819999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +837,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.138000000000005</v>
+        <v>68.197999999999993</v>
       </c>
       <c r="C34">
-        <v>3.577</v>
+        <v>3.5569999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +848,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>67.998999999999995</v>
+        <v>68.058999999999997</v>
       </c>
       <c r="C35">
-        <v>3.6269999999999998</v>
+        <v>3.6070000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +859,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>67.852999999999994</v>
+        <v>67.91</v>
       </c>
       <c r="C36">
-        <v>3.7810000000000001</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +870,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.677000000000007</v>
+        <v>67.727000000000004</v>
       </c>
       <c r="C37">
-        <v>4.3680000000000003</v>
+        <v>4.3390000000000004</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +881,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.503</v>
+        <v>67.557000000000002</v>
       </c>
       <c r="C38">
-        <v>4.7880000000000003</v>
+        <v>4.7610000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +892,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.343000000000004</v>
+        <v>67.403000000000006</v>
       </c>
       <c r="C39">
-        <v>4.3499999999999996</v>
+        <v>4.3310000000000004</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +903,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.197000000000003</v>
+        <v>67.260000000000005</v>
       </c>
       <c r="C40">
-        <v>3.4670000000000001</v>
+        <v>3.4460000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +914,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.069999999999993</v>
+        <v>67.134</v>
       </c>
       <c r="C41">
-        <v>3.1789999999999998</v>
+        <v>3.1659999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +925,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.926000000000002</v>
+        <v>66.971000000000004</v>
       </c>
       <c r="C42">
-        <v>3.1640000000000001</v>
+        <v>3.1480000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +936,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.751000000000005</v>
+        <v>66.787999999999997</v>
       </c>
       <c r="C43">
-        <v>3.2869999999999999</v>
+        <v>3.2709999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +947,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.59</v>
+        <v>66.64</v>
       </c>
       <c r="C44">
-        <v>3.492</v>
+        <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +958,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.444999999999993</v>
+        <v>66.491</v>
       </c>
       <c r="C45">
-        <v>3.5590000000000002</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +969,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.322000000000003</v>
+        <v>66.361999999999995</v>
       </c>
       <c r="C46">
-        <v>3.544</v>
+        <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +980,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.2</v>
+        <v>66.242999999999995</v>
       </c>
       <c r="C47">
-        <v>3.6</v>
+        <v>3.5790000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +991,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.045000000000002</v>
+        <v>66.094999999999999</v>
       </c>
       <c r="C48">
-        <v>3.7570000000000001</v>
+        <v>3.734</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +1002,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.876999999999995</v>
+        <v>65.924000000000007</v>
       </c>
       <c r="C49">
-        <v>4.3289999999999997</v>
+        <v>4.306</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +1013,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.716999999999999</v>
+        <v>65.757000000000005</v>
       </c>
       <c r="C50">
-        <v>4.774</v>
+        <v>4.7519999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +1024,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.594999999999999</v>
+        <v>65.635000000000005</v>
       </c>
       <c r="C51">
-        <v>4.3449999999999998</v>
+        <v>4.3259999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1035,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.486999999999995</v>
+        <v>65.52</v>
       </c>
       <c r="C52">
-        <v>3.4969999999999999</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1046,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.376999999999995</v>
+        <v>65.397000000000006</v>
       </c>
       <c r="C53">
-        <v>3.1179999999999999</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1057,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.215999999999994</v>
+        <v>65.236000000000004</v>
       </c>
       <c r="C54">
-        <v>3.0760000000000001</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1068,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.061999999999998</v>
+        <v>65.075999999999993</v>
       </c>
       <c r="C55">
-        <v>3.1890000000000001</v>
+        <v>3.1739999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1079,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.929000000000002</v>
+        <v>64.935000000000002</v>
       </c>
       <c r="C56" s="2">
-        <v>3.419</v>
+        <v>3.407</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,13 +1412,1267 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488D40D0-EFC6-4442-9CE6-FCCBA0A90699}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B2">
+        <v>64.019000000000005</v>
+      </c>
+      <c r="C2">
+        <v>2.919</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B3">
+        <v>63.533999999999999</v>
+      </c>
+      <c r="C3">
+        <v>2.9498000000000002</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B4">
+        <v>60.07</v>
+      </c>
+      <c r="C4">
+        <v>3.1211000000000002</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B5">
+        <v>59.478999999999999</v>
+      </c>
+      <c r="C5">
+        <v>3.7837999999999998</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B6">
+        <v>57.866</v>
+      </c>
+      <c r="C6">
+        <v>4.1501999999999999</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B7">
+        <v>60.26</v>
+      </c>
+      <c r="C7">
+        <v>7.7126000000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B8">
+        <v>64.522999999999996</v>
+      </c>
+      <c r="C8">
+        <v>3.8382000000000001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B9">
+        <v>90.997</v>
+      </c>
+      <c r="C9">
+        <v>3.0581999999999998</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B10">
+        <v>98.06</v>
+      </c>
+      <c r="C10">
+        <v>2.7736999999999998</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B11">
+        <v>98.513999999999996</v>
+      </c>
+      <c r="C11">
+        <v>2.8881999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B12">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="C12">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B13">
+        <v>79.22</v>
+      </c>
+      <c r="C13">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B14">
+        <v>82.34</v>
+      </c>
+      <c r="C14">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B15">
+        <v>82.950999999999993</v>
+      </c>
+      <c r="C15">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B16">
+        <v>81.165000000000006</v>
+      </c>
+      <c r="C16">
+        <v>2.8879999999999999</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46327</v>
+      </c>
+      <c r="B17">
+        <v>79.572999999999993</v>
+      </c>
+      <c r="C17">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46357</v>
+      </c>
+      <c r="B18">
+        <v>77.81</v>
+      </c>
+      <c r="C18">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46388</v>
+      </c>
+      <c r="B19">
+        <v>76.319000000000003</v>
+      </c>
+      <c r="C19">
+        <v>3.9369999999999998</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46419</v>
+      </c>
+      <c r="B20">
+        <v>75.319000000000003</v>
+      </c>
+      <c r="C20">
+        <v>3.593</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46447</v>
+      </c>
+      <c r="B21">
+        <v>74.311999999999998</v>
+      </c>
+      <c r="C21">
+        <v>2.9209999999999998</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46478</v>
+      </c>
+      <c r="B22">
+        <v>73.489999999999995</v>
+      </c>
+      <c r="C22">
+        <v>2.786</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>46508</v>
+      </c>
+      <c r="B23">
+        <v>72.899000000000001</v>
+      </c>
+      <c r="C23">
+        <v>2.8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>46539</v>
+      </c>
+      <c r="B24">
+        <v>72.36</v>
+      </c>
+      <c r="C24">
+        <v>2.9420000000000002</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>46569</v>
+      </c>
+      <c r="B25">
+        <v>71.846000000000004</v>
+      </c>
+      <c r="C25">
+        <v>3.15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46600</v>
+      </c>
+      <c r="B26">
+        <v>71.456000000000003</v>
+      </c>
+      <c r="C26">
+        <v>3.22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46631</v>
+      </c>
+      <c r="B27">
+        <v>71.082999999999998</v>
+      </c>
+      <c r="C27">
+        <v>3.206</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46661</v>
+      </c>
+      <c r="B28">
+        <v>70.766999999999996</v>
+      </c>
+      <c r="C28">
+        <v>3.2869999999999999</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>46692</v>
+      </c>
+      <c r="B29">
+        <v>70.468999999999994</v>
+      </c>
+      <c r="C29">
+        <v>3.5459999999999998</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>46722</v>
+      </c>
+      <c r="B30">
+        <v>70.131</v>
+      </c>
+      <c r="C30">
+        <v>4.1749999999999998</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46753</v>
+      </c>
+      <c r="B31">
+        <v>69.846000000000004</v>
+      </c>
+      <c r="C31">
+        <v>4.6210000000000004</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>46784</v>
+      </c>
+      <c r="B32">
+        <v>69.61</v>
+      </c>
+      <c r="C32">
+        <v>4.1829999999999998</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>46813</v>
+      </c>
+      <c r="B33">
+        <v>69.356999999999999</v>
+      </c>
+      <c r="C33">
+        <v>3.431</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>46844</v>
+      </c>
+      <c r="B34">
+        <v>69.16</v>
+      </c>
+      <c r="C34">
+        <v>3.181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>46874</v>
+      </c>
+      <c r="B35">
+        <v>68.972999999999999</v>
+      </c>
+      <c r="C35">
+        <v>3.169</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46905</v>
+      </c>
+      <c r="B36">
+        <v>68.739999999999995</v>
+      </c>
+      <c r="C36">
+        <v>3.32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>46935</v>
+      </c>
+      <c r="B37">
+        <v>68.546999999999997</v>
+      </c>
+      <c r="C37">
+        <v>3.5209999999999999</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>46966</v>
+      </c>
+      <c r="B38">
+        <v>68.375</v>
+      </c>
+      <c r="C38">
+        <v>3.5819999999999999</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>46997</v>
+      </c>
+      <c r="B39">
+        <v>68.197999999999993</v>
+      </c>
+      <c r="C39">
+        <v>3.5569999999999999</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>47027</v>
+      </c>
+      <c r="B40">
+        <v>68.058999999999997</v>
+      </c>
+      <c r="C40">
+        <v>3.6070000000000002</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>47058</v>
+      </c>
+      <c r="B41">
+        <v>67.91</v>
+      </c>
+      <c r="C41">
+        <v>3.76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>47088</v>
+      </c>
+      <c r="B42">
+        <v>67.727000000000004</v>
+      </c>
+      <c r="C42">
+        <v>4.3390000000000004</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>47119</v>
+      </c>
+      <c r="B43">
+        <v>67.557000000000002</v>
+      </c>
+      <c r="C43">
+        <v>4.7610000000000001</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>47150</v>
+      </c>
+      <c r="B44">
+        <v>67.403000000000006</v>
+      </c>
+      <c r="C44">
+        <v>4.3310000000000004</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>47178</v>
+      </c>
+      <c r="B45">
+        <v>67.260000000000005</v>
+      </c>
+      <c r="C45">
+        <v>3.4460000000000002</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>47209</v>
+      </c>
+      <c r="B46">
+        <v>67.134</v>
+      </c>
+      <c r="C46">
+        <v>3.1659999999999999</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>47239</v>
+      </c>
+      <c r="B47">
+        <v>66.971000000000004</v>
+      </c>
+      <c r="C47">
+        <v>3.1480000000000001</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47270</v>
+      </c>
+      <c r="B48">
+        <v>66.787999999999997</v>
+      </c>
+      <c r="C48">
+        <v>3.2709999999999999</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47300</v>
+      </c>
+      <c r="B49">
+        <v>66.64</v>
+      </c>
+      <c r="C49">
+        <v>3.4740000000000002</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>47331</v>
+      </c>
+      <c r="B50">
+        <v>66.491</v>
+      </c>
+      <c r="C50">
+        <v>3.54</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47362</v>
+      </c>
+      <c r="B51">
+        <v>66.361999999999995</v>
+      </c>
+      <c r="C51">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>47392</v>
+      </c>
+      <c r="B52">
+        <v>66.242999999999995</v>
+      </c>
+      <c r="C52">
+        <v>3.5790000000000002</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>47423</v>
+      </c>
+      <c r="B53">
+        <v>66.094999999999999</v>
+      </c>
+      <c r="C53">
+        <v>3.734</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>47453</v>
+      </c>
+      <c r="B54">
+        <v>65.924000000000007</v>
+      </c>
+      <c r="C54">
+        <v>4.306</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>47484</v>
+      </c>
+      <c r="B55">
+        <v>65.757000000000005</v>
+      </c>
+      <c r="C55">
+        <v>4.7519999999999998</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>47515</v>
+      </c>
+      <c r="B56">
+        <v>65.635000000000005</v>
+      </c>
+      <c r="C56">
+        <v>4.3259999999999996</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>47543</v>
+      </c>
+      <c r="B57">
+        <v>65.52</v>
+      </c>
+      <c r="C57">
+        <v>3.48</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>47574</v>
+      </c>
+      <c r="B58">
+        <v>65.397000000000006</v>
+      </c>
+      <c r="C58">
+        <v>3.101</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>47604</v>
+      </c>
+      <c r="B59">
+        <v>65.236000000000004</v>
+      </c>
+      <c r="C59">
+        <v>3.06</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>47635</v>
+      </c>
+      <c r="B60">
+        <v>65.075999999999993</v>
+      </c>
+      <c r="C60">
+        <v>3.1739999999999999</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>47665</v>
+      </c>
+      <c r="B61">
+        <v>64.935000000000002</v>
+      </c>
+      <c r="C61">
+        <v>3.407</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46262</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1688,42 +2971,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1748,12 +3010,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBDD28FD-DE88-4884-A202-035D994C2181}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C45BF3-8911-49E1-8548-659367AF2BDD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>oil_price</t>
   </si>
@@ -43,33 +42,6 @@
   </si>
   <si>
     <t>gas_price</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>WTI</t>
-  </si>
-  <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>SourceWTI</t>
-  </si>
-  <si>
-    <t>SourceHH</t>
-  </si>
-  <si>
-    <t>MaxAsOfDate</t>
-  </si>
-  <si>
-    <t>SETTLED</t>
-  </si>
-  <si>
-    <t>STRIP</t>
-  </si>
-  <si>
-    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -107,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -122,7 +94,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +533,7 @@
         <v>46235</v>
       </c>
       <c r="B9">
-        <v>82.34</v>
+        <v>82.451999999999998</v>
       </c>
       <c r="C9">
         <v>2.9386999999999999</v>
@@ -573,7 +544,7 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>82.950999999999993</v>
+        <v>85.274000000000001</v>
       </c>
       <c r="C10">
         <v>2.9386999999999999</v>
@@ -584,10 +555,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>81.165000000000006</v>
+        <v>83.335999999999999</v>
       </c>
       <c r="C11">
-        <v>2.8879999999999999</v>
+        <v>2.9350000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -595,10 +566,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>79.572999999999993</v>
+        <v>81.582999999999998</v>
       </c>
       <c r="C12">
-        <v>3.0350000000000001</v>
+        <v>3.0640000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -606,10 +577,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>77.81</v>
+        <v>79.557000000000002</v>
       </c>
       <c r="C13">
-        <v>3.5249999999999999</v>
+        <v>3.5179999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,10 +588,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>76.319000000000003</v>
+        <v>77.808000000000007</v>
       </c>
       <c r="C14">
-        <v>3.9369999999999998</v>
+        <v>3.9430000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,10 +599,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>75.319000000000003</v>
+        <v>76.632000000000005</v>
       </c>
       <c r="C15">
-        <v>3.593</v>
+        <v>3.5939999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +610,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>74.311999999999998</v>
+        <v>75.444000000000003</v>
       </c>
       <c r="C16">
-        <v>2.9209999999999998</v>
+        <v>2.9159999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +621,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>73.489999999999995</v>
+        <v>74.483999999999995</v>
       </c>
       <c r="C17">
-        <v>2.786</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +632,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>72.899000000000001</v>
+        <v>73.802000000000007</v>
       </c>
       <c r="C18">
-        <v>2.8</v>
+        <v>2.7890000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +643,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>72.36</v>
+        <v>73.174000000000007</v>
       </c>
       <c r="C19">
-        <v>2.9420000000000002</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,10 +654,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>71.846000000000004</v>
+        <v>72.566000000000003</v>
       </c>
       <c r="C20">
-        <v>3.15</v>
+        <v>3.1379999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,10 +665,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>71.456000000000003</v>
+        <v>72.106999999999999</v>
       </c>
       <c r="C21">
-        <v>3.22</v>
+        <v>3.2090000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,10 +676,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>71.082999999999998</v>
+        <v>71.673000000000002</v>
       </c>
       <c r="C22">
-        <v>3.206</v>
+        <v>3.1960000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +687,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>70.766999999999996</v>
+        <v>71.307000000000002</v>
       </c>
       <c r="C23">
-        <v>3.2869999999999999</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +698,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.468999999999994</v>
+        <v>70.98</v>
       </c>
       <c r="C24">
-        <v>3.5459999999999998</v>
+        <v>3.5419999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +709,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.131</v>
+        <v>70.61</v>
       </c>
       <c r="C25">
-        <v>4.1749999999999998</v>
+        <v>4.1660000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +720,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>69.846000000000004</v>
+        <v>70.295000000000002</v>
       </c>
       <c r="C26">
-        <v>4.6210000000000004</v>
+        <v>4.6120000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +731,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>69.61</v>
+        <v>70.033000000000001</v>
       </c>
       <c r="C27">
-        <v>4.1829999999999998</v>
+        <v>4.1840000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +742,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.356999999999999</v>
+        <v>69.747</v>
       </c>
       <c r="C28">
-        <v>3.431</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +753,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.16</v>
+        <v>69.521000000000001</v>
       </c>
       <c r="C29">
-        <v>3.181</v>
+        <v>3.1749999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -793,10 +764,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>68.972999999999999</v>
+        <v>69.307000000000002</v>
       </c>
       <c r="C30">
-        <v>3.169</v>
+        <v>3.1629999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,10 +775,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>68.739999999999995</v>
+        <v>69.052000000000007</v>
       </c>
       <c r="C31">
-        <v>3.32</v>
+        <v>3.3140000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -815,10 +786,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.546999999999997</v>
+        <v>68.832999999999998</v>
       </c>
       <c r="C32">
-        <v>3.5209999999999999</v>
+        <v>3.5150000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,10 +797,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.375</v>
+        <v>68.626000000000005</v>
       </c>
       <c r="C33">
-        <v>3.5819999999999999</v>
+        <v>3.577</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,10 +808,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.197999999999993</v>
+        <v>68.417000000000002</v>
       </c>
       <c r="C34">
-        <v>3.5569999999999999</v>
+        <v>3.5510000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,10 +819,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.058999999999997</v>
+        <v>68.251999999999995</v>
       </c>
       <c r="C35">
-        <v>3.6070000000000002</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -859,10 +830,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>67.91</v>
+        <v>68.082999999999998</v>
       </c>
       <c r="C36">
-        <v>3.76</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,10 +841,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.727000000000004</v>
+        <v>67.876999999999995</v>
       </c>
       <c r="C37">
-        <v>4.3390000000000004</v>
+        <v>4.3259999999999996</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,10 +852,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.557000000000002</v>
+        <v>67.680000000000007</v>
       </c>
       <c r="C38">
-        <v>4.7610000000000001</v>
+        <v>4.758</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,10 +863,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.403000000000006</v>
+        <v>67.506</v>
       </c>
       <c r="C39">
-        <v>4.3310000000000004</v>
+        <v>4.3250000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +874,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.260000000000005</v>
+        <v>67.332999999999998</v>
       </c>
       <c r="C40">
-        <v>3.4460000000000002</v>
+        <v>3.4420000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +885,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.134</v>
+        <v>67.174000000000007</v>
       </c>
       <c r="C41">
-        <v>3.1659999999999999</v>
+        <v>3.1629999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +896,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.971000000000004</v>
+        <v>67.010999999999996</v>
       </c>
       <c r="C42">
-        <v>3.1480000000000001</v>
+        <v>3.145</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,10 +907,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.787999999999997</v>
+        <v>66.816999999999993</v>
       </c>
       <c r="C43">
-        <v>3.2709999999999999</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,7 +918,7 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.64</v>
+        <v>66.643000000000001</v>
       </c>
       <c r="C44">
         <v>3.4740000000000002</v>
@@ -958,10 +929,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.491</v>
+        <v>66.474000000000004</v>
       </c>
       <c r="C45">
-        <v>3.54</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,10 +940,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.361999999999995</v>
+        <v>66.325999999999993</v>
       </c>
       <c r="C46">
-        <v>3.5249999999999999</v>
+        <v>3.5209999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,10 +951,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.242999999999995</v>
+        <v>66.180999999999997</v>
       </c>
       <c r="C47">
-        <v>3.5790000000000002</v>
+        <v>3.5750000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -991,10 +962,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.094999999999999</v>
+        <v>65.994</v>
       </c>
       <c r="C48">
-        <v>3.734</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1002,10 +973,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.924000000000007</v>
+        <v>65.8</v>
       </c>
       <c r="C49">
-        <v>4.306</v>
+        <v>4.2939999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,10 +984,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.757000000000005</v>
+        <v>65.62</v>
       </c>
       <c r="C50">
-        <v>4.7519999999999998</v>
+        <v>4.7450000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,10 +995,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.635000000000005</v>
+        <v>65.478999999999999</v>
       </c>
       <c r="C51">
-        <v>4.3259999999999996</v>
+        <v>4.3209999999999997</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,10 +1006,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.52</v>
+        <v>65.343000000000004</v>
       </c>
       <c r="C52">
-        <v>3.48</v>
+        <v>3.4769999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,10 +1017,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.397000000000006</v>
+        <v>65.200999999999993</v>
       </c>
       <c r="C53">
-        <v>3.101</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,10 +1028,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.236000000000004</v>
+        <v>65.02</v>
       </c>
       <c r="C54">
-        <v>3.06</v>
+        <v>3.0569999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,10 +1039,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.075999999999993</v>
+        <v>64.838999999999999</v>
       </c>
       <c r="C55">
-        <v>3.1739999999999999</v>
+        <v>3.1720000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,10 +1050,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.935000000000002</v>
+        <v>64.679000000000002</v>
       </c>
       <c r="C56" s="2">
-        <v>3.407</v>
+        <v>3.4060000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1090,10 +1061,10 @@
         <v>47696</v>
       </c>
       <c r="B57" s="2">
-        <v>64.814999999999998</v>
+        <v>64.519000000000005</v>
       </c>
       <c r="C57" s="2">
-        <v>3.444</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1409,1236 +1380,6 @@
   <ignoredErrors>
     <ignoredError sqref="A57:A85 A2:A55 A56" numberStoredAsText="1"/>
   </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488D40D0-EFC6-4442-9CE6-FCCBA0A90699}">
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>45870</v>
-      </c>
-      <c r="B2">
-        <v>64.019000000000005</v>
-      </c>
-      <c r="C2">
-        <v>2.919</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B3">
-        <v>63.533999999999999</v>
-      </c>
-      <c r="C3">
-        <v>2.9498000000000002</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B4">
-        <v>60.07</v>
-      </c>
-      <c r="C4">
-        <v>3.1211000000000002</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>45962</v>
-      </c>
-      <c r="B5">
-        <v>59.478999999999999</v>
-      </c>
-      <c r="C5">
-        <v>3.7837999999999998</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>45992</v>
-      </c>
-      <c r="B6">
-        <v>57.866</v>
-      </c>
-      <c r="C6">
-        <v>4.1501999999999999</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B7">
-        <v>60.26</v>
-      </c>
-      <c r="C7">
-        <v>7.7126000000000001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B8">
-        <v>64.522999999999996</v>
-      </c>
-      <c r="C8">
-        <v>3.8382000000000001</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>46082</v>
-      </c>
-      <c r="B9">
-        <v>90.997</v>
-      </c>
-      <c r="C9">
-        <v>3.0581999999999998</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B10">
-        <v>98.06</v>
-      </c>
-      <c r="C10">
-        <v>2.7736999999999998</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B11">
-        <v>98.513999999999996</v>
-      </c>
-      <c r="C11">
-        <v>2.8881999999999999</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B12">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="C12">
-        <v>3.1429999999999998</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>46204</v>
-      </c>
-      <c r="B13">
-        <v>79.22</v>
-      </c>
-      <c r="C13">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B14">
-        <v>82.34</v>
-      </c>
-      <c r="C14">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46266</v>
-      </c>
-      <c r="B15">
-        <v>82.950999999999993</v>
-      </c>
-      <c r="C15">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>46296</v>
-      </c>
-      <c r="B16">
-        <v>81.165000000000006</v>
-      </c>
-      <c r="C16">
-        <v>2.8879999999999999</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>46327</v>
-      </c>
-      <c r="B17">
-        <v>79.572999999999993</v>
-      </c>
-      <c r="C17">
-        <v>3.0350000000000001</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>46357</v>
-      </c>
-      <c r="B18">
-        <v>77.81</v>
-      </c>
-      <c r="C18">
-        <v>3.5249999999999999</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>46388</v>
-      </c>
-      <c r="B19">
-        <v>76.319000000000003</v>
-      </c>
-      <c r="C19">
-        <v>3.9369999999999998</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46419</v>
-      </c>
-      <c r="B20">
-        <v>75.319000000000003</v>
-      </c>
-      <c r="C20">
-        <v>3.593</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>46447</v>
-      </c>
-      <c r="B21">
-        <v>74.311999999999998</v>
-      </c>
-      <c r="C21">
-        <v>2.9209999999999998</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>46478</v>
-      </c>
-      <c r="B22">
-        <v>73.489999999999995</v>
-      </c>
-      <c r="C22">
-        <v>2.786</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>46508</v>
-      </c>
-      <c r="B23">
-        <v>72.899000000000001</v>
-      </c>
-      <c r="C23">
-        <v>2.8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46539</v>
-      </c>
-      <c r="B24">
-        <v>72.36</v>
-      </c>
-      <c r="C24">
-        <v>2.9420000000000002</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>46569</v>
-      </c>
-      <c r="B25">
-        <v>71.846000000000004</v>
-      </c>
-      <c r="C25">
-        <v>3.15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>46600</v>
-      </c>
-      <c r="B26">
-        <v>71.456000000000003</v>
-      </c>
-      <c r="C26">
-        <v>3.22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>46631</v>
-      </c>
-      <c r="B27">
-        <v>71.082999999999998</v>
-      </c>
-      <c r="C27">
-        <v>3.206</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>46661</v>
-      </c>
-      <c r="B28">
-        <v>70.766999999999996</v>
-      </c>
-      <c r="C28">
-        <v>3.2869999999999999</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>46692</v>
-      </c>
-      <c r="B29">
-        <v>70.468999999999994</v>
-      </c>
-      <c r="C29">
-        <v>3.5459999999999998</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>46722</v>
-      </c>
-      <c r="B30">
-        <v>70.131</v>
-      </c>
-      <c r="C30">
-        <v>4.1749999999999998</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>46753</v>
-      </c>
-      <c r="B31">
-        <v>69.846000000000004</v>
-      </c>
-      <c r="C31">
-        <v>4.6210000000000004</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>46784</v>
-      </c>
-      <c r="B32">
-        <v>69.61</v>
-      </c>
-      <c r="C32">
-        <v>4.1829999999999998</v>
-      </c>
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>46813</v>
-      </c>
-      <c r="B33">
-        <v>69.356999999999999</v>
-      </c>
-      <c r="C33">
-        <v>3.431</v>
-      </c>
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>46844</v>
-      </c>
-      <c r="B34">
-        <v>69.16</v>
-      </c>
-      <c r="C34">
-        <v>3.181</v>
-      </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>46874</v>
-      </c>
-      <c r="B35">
-        <v>68.972999999999999</v>
-      </c>
-      <c r="C35">
-        <v>3.169</v>
-      </c>
-      <c r="D35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>46905</v>
-      </c>
-      <c r="B36">
-        <v>68.739999999999995</v>
-      </c>
-      <c r="C36">
-        <v>3.32</v>
-      </c>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>46935</v>
-      </c>
-      <c r="B37">
-        <v>68.546999999999997</v>
-      </c>
-      <c r="C37">
-        <v>3.5209999999999999</v>
-      </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>46966</v>
-      </c>
-      <c r="B38">
-        <v>68.375</v>
-      </c>
-      <c r="C38">
-        <v>3.5819999999999999</v>
-      </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>46997</v>
-      </c>
-      <c r="B39">
-        <v>68.197999999999993</v>
-      </c>
-      <c r="C39">
-        <v>3.5569999999999999</v>
-      </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>47027</v>
-      </c>
-      <c r="B40">
-        <v>68.058999999999997</v>
-      </c>
-      <c r="C40">
-        <v>3.6070000000000002</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>47058</v>
-      </c>
-      <c r="B41">
-        <v>67.91</v>
-      </c>
-      <c r="C41">
-        <v>3.76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>47088</v>
-      </c>
-      <c r="B42">
-        <v>67.727000000000004</v>
-      </c>
-      <c r="C42">
-        <v>4.3390000000000004</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>47119</v>
-      </c>
-      <c r="B43">
-        <v>67.557000000000002</v>
-      </c>
-      <c r="C43">
-        <v>4.7610000000000001</v>
-      </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>47150</v>
-      </c>
-      <c r="B44">
-        <v>67.403000000000006</v>
-      </c>
-      <c r="C44">
-        <v>4.3310000000000004</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>47178</v>
-      </c>
-      <c r="B45">
-        <v>67.260000000000005</v>
-      </c>
-      <c r="C45">
-        <v>3.4460000000000002</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>47209</v>
-      </c>
-      <c r="B46">
-        <v>67.134</v>
-      </c>
-      <c r="C46">
-        <v>3.1659999999999999</v>
-      </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>47239</v>
-      </c>
-      <c r="B47">
-        <v>66.971000000000004</v>
-      </c>
-      <c r="C47">
-        <v>3.1480000000000001</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>47270</v>
-      </c>
-      <c r="B48">
-        <v>66.787999999999997</v>
-      </c>
-      <c r="C48">
-        <v>3.2709999999999999</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>47300</v>
-      </c>
-      <c r="B49">
-        <v>66.64</v>
-      </c>
-      <c r="C49">
-        <v>3.4740000000000002</v>
-      </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>47331</v>
-      </c>
-      <c r="B50">
-        <v>66.491</v>
-      </c>
-      <c r="C50">
-        <v>3.54</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>47362</v>
-      </c>
-      <c r="B51">
-        <v>66.361999999999995</v>
-      </c>
-      <c r="C51">
-        <v>3.5249999999999999</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>47392</v>
-      </c>
-      <c r="B52">
-        <v>66.242999999999995</v>
-      </c>
-      <c r="C52">
-        <v>3.5790000000000002</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>47423</v>
-      </c>
-      <c r="B53">
-        <v>66.094999999999999</v>
-      </c>
-      <c r="C53">
-        <v>3.734</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>47453</v>
-      </c>
-      <c r="B54">
-        <v>65.924000000000007</v>
-      </c>
-      <c r="C54">
-        <v>4.306</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>47484</v>
-      </c>
-      <c r="B55">
-        <v>65.757000000000005</v>
-      </c>
-      <c r="C55">
-        <v>4.7519999999999998</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>47515</v>
-      </c>
-      <c r="B56">
-        <v>65.635000000000005</v>
-      </c>
-      <c r="C56">
-        <v>4.3259999999999996</v>
-      </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>47543</v>
-      </c>
-      <c r="B57">
-        <v>65.52</v>
-      </c>
-      <c r="C57">
-        <v>3.48</v>
-      </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>47574</v>
-      </c>
-      <c r="B58">
-        <v>65.397000000000006</v>
-      </c>
-      <c r="C58">
-        <v>3.101</v>
-      </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>47604</v>
-      </c>
-      <c r="B59">
-        <v>65.236000000000004</v>
-      </c>
-      <c r="C59">
-        <v>3.06</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>47635</v>
-      </c>
-      <c r="B60">
-        <v>65.075999999999993</v>
-      </c>
-      <c r="C60">
-        <v>3.1739999999999999</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>47665</v>
-      </c>
-      <c r="B61">
-        <v>64.935000000000002</v>
-      </c>
-      <c r="C61">
-        <v>3.407</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="6">
-        <v>46262</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2676,6 +1417,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -2970,15 +1720,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
@@ -2991,6 +1732,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3007,12 +1756,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C45BF3-8911-49E1-8548-659367AF2BDD}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94398809-E5ED-4E70-9DF4-7B00855FAE8C}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19305" yWindow="135" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -431,16 +431,38 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{34422C33-4607-49AE-BA63-7B417D302868}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;f2d25c0e-17ed-456c-8c11-70f41c22c2e5&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -451,7 +473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>46023</v>
       </c>
@@ -462,7 +484,7 @@
         <v>4.6870000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
@@ -473,7 +495,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>46082</v>
       </c>
@@ -484,7 +506,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>46113</v>
       </c>
@@ -495,7 +517,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>46143</v>
       </c>
@@ -506,7 +528,7 @@
         <v>2.8881999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>46174</v>
       </c>
@@ -517,7 +539,7 @@
         <v>3.1429999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>46204</v>
       </c>
@@ -528,7 +550,7 @@
         <v>2.9386999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>46235</v>
       </c>
@@ -536,538 +558,538 @@
         <v>82.451999999999998</v>
       </c>
       <c r="C9">
-        <v>2.9386999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9213499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>85.274000000000001</v>
+        <v>89.513999999999996</v>
       </c>
       <c r="C10">
-        <v>2.9386999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9213499999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>83.335999999999999</v>
+        <v>86.739000000000004</v>
       </c>
       <c r="C11">
-        <v>2.9350000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9039999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>81.582999999999998</v>
+        <v>84.328000000000003</v>
       </c>
       <c r="C12">
-        <v>3.0640000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.0339999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>79.557000000000002</v>
+        <v>81.686999999999998</v>
       </c>
       <c r="C13">
-        <v>3.5179999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.4929999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>77.808000000000007</v>
+        <v>79.489000000000004</v>
       </c>
       <c r="C14">
-        <v>3.9430000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.9159999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>76.632000000000005</v>
+        <v>78.034999999999997</v>
       </c>
       <c r="C15">
-        <v>3.5939999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5739999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>75.444000000000003</v>
+        <v>76.573999999999998</v>
       </c>
       <c r="C16">
-        <v>2.9159999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9009999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>74.483999999999995</v>
+        <v>75.399000000000001</v>
       </c>
       <c r="C17">
-        <v>2.778</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>73.802000000000007</v>
+        <v>74.591999999999999</v>
       </c>
       <c r="C18">
-        <v>2.7890000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.7850000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>73.174000000000007</v>
+        <v>73.869</v>
       </c>
       <c r="C19">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9289999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>72.566000000000003</v>
+        <v>73.180000000000007</v>
       </c>
       <c r="C20">
-        <v>3.1379999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>72.106999999999999</v>
+        <v>72.683999999999997</v>
       </c>
       <c r="C21">
-        <v>3.2090000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.2149999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>71.673000000000002</v>
+        <v>72.212999999999994</v>
       </c>
       <c r="C22">
-        <v>3.1960000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>71.307000000000002</v>
+        <v>71.816999999999993</v>
       </c>
       <c r="C23">
-        <v>3.278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.2829999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>70.98</v>
+        <v>71.460999999999999</v>
       </c>
       <c r="C24">
-        <v>3.5419999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5449999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>70.61</v>
+        <v>71.058999999999997</v>
       </c>
       <c r="C25">
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>70.295000000000002</v>
+        <v>70.715000000000003</v>
       </c>
       <c r="C26">
-        <v>4.6120000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.6109999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.033000000000001</v>
+        <v>70.424999999999997</v>
       </c>
       <c r="C27">
-        <v>4.1840000000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.1829999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>69.747</v>
+        <v>70.113</v>
       </c>
       <c r="C28">
-        <v>3.427</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.4220000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.521000000000001</v>
+        <v>69.876999999999995</v>
       </c>
       <c r="C29">
-        <v>3.1749999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.1709999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>69.307000000000002</v>
+        <v>69.652000000000001</v>
       </c>
       <c r="C30">
-        <v>3.1629999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.052000000000007</v>
+        <v>69.375</v>
       </c>
       <c r="C31">
-        <v>3.3140000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.3119999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>68.832999999999998</v>
+        <v>69.14</v>
       </c>
       <c r="C32">
-        <v>3.5150000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5139999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.626000000000005</v>
+        <v>68.926000000000002</v>
       </c>
       <c r="C33">
-        <v>3.577</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5760000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.417000000000002</v>
+        <v>68.716999999999999</v>
       </c>
       <c r="C34">
-        <v>3.5510000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.251999999999995</v>
+        <v>68.543000000000006</v>
       </c>
       <c r="C35">
         <v>3.601</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.082999999999998</v>
+        <v>68.346999999999994</v>
       </c>
       <c r="C36">
-        <v>3.754</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.7519999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.876999999999995</v>
+        <v>68.123000000000005</v>
       </c>
       <c r="C37">
-        <v>4.3259999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.3170000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.680000000000007</v>
+        <v>67.917000000000002</v>
       </c>
       <c r="C38">
-        <v>4.758</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.7640000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.506</v>
+        <v>67.733000000000004</v>
       </c>
       <c r="C39">
-        <v>4.3250000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.332999999999998</v>
+        <v>67.552999999999997</v>
       </c>
       <c r="C40">
-        <v>3.4420000000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.4470000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.174000000000007</v>
+        <v>67.394000000000005</v>
       </c>
       <c r="C41">
-        <v>3.1629999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.1619999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.010999999999996</v>
+        <v>67.224999999999994</v>
       </c>
       <c r="C42">
-        <v>3.145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.1440000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.816999999999993</v>
+        <v>67.013999999999996</v>
       </c>
       <c r="C43">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.2690000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.643000000000001</v>
+        <v>66.83</v>
       </c>
       <c r="C44">
-        <v>3.4740000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.474000000000004</v>
+        <v>66.653999999999996</v>
       </c>
       <c r="C45">
-        <v>3.5369999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5350000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.325999999999993</v>
+        <v>66.503</v>
       </c>
       <c r="C46">
-        <v>3.5209999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.180999999999997</v>
+        <v>66.353999999999999</v>
       </c>
       <c r="C47">
-        <v>3.5750000000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.5760000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.994</v>
+        <v>66.174000000000007</v>
       </c>
       <c r="C48">
-        <v>3.726</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.7269999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.8</v>
+        <v>65.977000000000004</v>
       </c>
       <c r="C49">
-        <v>4.2939999999999996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.2869999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.62</v>
+        <v>65.787000000000006</v>
       </c>
       <c r="C50">
-        <v>4.7450000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.7480000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.478999999999999</v>
+        <v>65.635999999999996</v>
       </c>
       <c r="C51">
-        <v>4.3209999999999997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4.3239999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.343000000000004</v>
+        <v>65.492999999999995</v>
       </c>
       <c r="C52">
-        <v>3.4769999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.4790000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.200999999999993</v>
+        <v>65.349000000000004</v>
       </c>
       <c r="C53">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.1019999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.02</v>
+        <v>65.156000000000006</v>
       </c>
       <c r="C54">
-        <v>3.0569999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.0579999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.838999999999999</v>
+        <v>64.968999999999994</v>
       </c>
       <c r="C55">
-        <v>3.1720000000000002</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>47665</v>
       </c>
-      <c r="B56" s="2">
-        <v>64.679000000000002</v>
-      </c>
-      <c r="C56" s="2">
-        <v>3.4060000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>64.808999999999997</v>
+      </c>
+      <c r="C56">
+        <v>3.407</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>47696</v>
       </c>
-      <c r="B57" s="2">
-        <v>64.519000000000005</v>
-      </c>
-      <c r="C57" s="2">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>64.644999999999996</v>
+      </c>
+      <c r="C57">
+        <v>3.4510000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>47727</v>
       </c>
@@ -1078,7 +1100,7 @@
         <v>3.4209999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>47757</v>
       </c>
@@ -1089,7 +1111,7 @@
         <v>3.4969999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>47788</v>
       </c>
@@ -1100,7 +1122,7 @@
         <v>3.6549999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>47818</v>
       </c>
@@ -1111,7 +1133,7 @@
         <v>4.2039999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>47849</v>
       </c>
@@ -1122,7 +1144,7 @@
         <v>4.625</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>47880</v>
       </c>
@@ -1133,7 +1155,7 @@
         <v>4.2160000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>47908</v>
       </c>
@@ -1144,7 +1166,7 @@
         <v>3.4260000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>47939</v>
       </c>
@@ -1155,7 +1177,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>47969</v>
       </c>
@@ -1166,7 +1188,7 @@
         <v>3.0139999999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>48000</v>
       </c>
@@ -1177,7 +1199,7 @@
         <v>3.1360000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>48030</v>
       </c>
@@ -1188,7 +1210,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>48061</v>
       </c>
@@ -1199,7 +1221,7 @@
         <v>3.4180000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>48092</v>
       </c>
@@ -1210,7 +1232,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>48122</v>
       </c>
@@ -1221,7 +1243,7 @@
         <v>3.4860000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>48153</v>
       </c>
@@ -1232,7 +1254,7 @@
         <v>3.7149999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>48183</v>
       </c>
@@ -1243,7 +1265,7 @@
         <v>4.3179999999999996</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>48214</v>
       </c>
@@ -1254,7 +1276,7 @@
         <v>4.6550000000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>48245</v>
       </c>
@@ -1265,7 +1287,7 @@
         <v>4.2469999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>48274</v>
       </c>
@@ -1276,7 +1298,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>48305</v>
       </c>
@@ -1287,7 +1309,7 @@
         <v>2.968</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>48335</v>
       </c>
@@ -1298,7 +1320,7 @@
         <v>2.9359999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>48366</v>
       </c>
@@ -1309,7 +1331,7 @@
         <v>3.0510000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>48396</v>
       </c>
@@ -1320,7 +1342,7 @@
         <v>3.2320000000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>48427</v>
       </c>
@@ -1331,7 +1353,7 @@
         <v>3.2839999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>48458</v>
       </c>
@@ -1342,7 +1364,7 @@
         <v>3.2589999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>48488</v>
       </c>
@@ -1353,7 +1375,7 @@
         <v>3.3239999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>48519</v>
       </c>
@@ -1364,7 +1386,7 @@
         <v>3.5390000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>48549</v>
       </c>
@@ -1384,39 +1406,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1425,7 +1414,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1720,18 +1709,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1739,7 +1750,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1756,4 +1767,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94398809-E5ED-4E70-9DF4-7B00855FAE8C}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED465A7-7FC3-49C9-9436-67986F33AF3B}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="135" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
   <si>
     <t>oil_price</t>
   </si>
@@ -42,6 +43,33 @@
   </si>
   <si>
     <t>gas_price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>WTI</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>SourceWTI</t>
+  </si>
+  <si>
+    <t>SourceHH</t>
+  </si>
+  <si>
+    <t>MaxAsOfDate</t>
+  </si>
+  <si>
+    <t>SETTLED</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>STRIP</t>
   </si>
 </sst>
 </file>
@@ -79,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -94,6 +122,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,13 +485,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="5" customWidth="1"/>
-    <col min="2" max="3" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -473,7 +502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>46023</v>
       </c>
@@ -484,7 +513,7 @@
         <v>4.6870000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
@@ -495,7 +524,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46082</v>
       </c>
@@ -506,7 +535,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46113</v>
       </c>
@@ -517,7 +546,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46143</v>
       </c>
@@ -528,7 +557,7 @@
         <v>2.8881999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46174</v>
       </c>
@@ -539,7 +568,7 @@
         <v>3.1429999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46204</v>
       </c>
@@ -550,7 +579,7 @@
         <v>2.9386999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46235</v>
       </c>
@@ -561,7 +590,7 @@
         <v>2.9213499999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46266</v>
       </c>
@@ -572,7 +601,7 @@
         <v>2.9213499999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46296</v>
       </c>
@@ -583,7 +612,7 @@
         <v>2.9039999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46327</v>
       </c>
@@ -594,7 +623,7 @@
         <v>3.0339999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46357</v>
       </c>
@@ -605,7 +634,7 @@
         <v>3.4929999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46388</v>
       </c>
@@ -616,7 +645,7 @@
         <v>3.9159999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46419</v>
       </c>
@@ -627,7 +656,7 @@
         <v>3.5739999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46447</v>
       </c>
@@ -638,7 +667,7 @@
         <v>2.9009999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46478</v>
       </c>
@@ -649,7 +678,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46508</v>
       </c>
@@ -660,7 +689,7 @@
         <v>2.7850000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46539</v>
       </c>
@@ -671,7 +700,7 @@
         <v>2.9289999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46569</v>
       </c>
@@ -682,7 +711,7 @@
         <v>3.141</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>46600</v>
       </c>
@@ -693,7 +722,7 @@
         <v>3.2149999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46631</v>
       </c>
@@ -704,7 +733,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46661</v>
       </c>
@@ -715,7 +744,7 @@
         <v>3.2829999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46692</v>
       </c>
@@ -726,7 +755,7 @@
         <v>3.5449999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46722</v>
       </c>
@@ -737,7 +766,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>46753</v>
       </c>
@@ -748,7 +777,7 @@
         <v>4.6109999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46784</v>
       </c>
@@ -759,7 +788,7 @@
         <v>4.1829999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>46813</v>
       </c>
@@ -770,7 +799,7 @@
         <v>3.4220000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>46844</v>
       </c>
@@ -781,7 +810,7 @@
         <v>3.1709999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46874</v>
       </c>
@@ -792,7 +821,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>46905</v>
       </c>
@@ -803,7 +832,7 @@
         <v>3.3119999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46935</v>
       </c>
@@ -814,7 +843,7 @@
         <v>3.5139999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>46966</v>
       </c>
@@ -825,7 +854,7 @@
         <v>3.5760000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>46997</v>
       </c>
@@ -836,7 +865,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>47027</v>
       </c>
@@ -847,7 +876,7 @@
         <v>3.601</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>47058</v>
       </c>
@@ -858,7 +887,7 @@
         <v>3.7519999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>47088</v>
       </c>
@@ -869,7 +898,7 @@
         <v>4.3170000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>47119</v>
       </c>
@@ -880,7 +909,7 @@
         <v>4.7640000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>47150</v>
       </c>
@@ -891,7 +920,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>47178</v>
       </c>
@@ -902,7 +931,7 @@
         <v>3.4470000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>47209</v>
       </c>
@@ -913,7 +942,7 @@
         <v>3.1619999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>47239</v>
       </c>
@@ -924,7 +953,7 @@
         <v>3.1440000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>47270</v>
       </c>
@@ -935,7 +964,7 @@
         <v>3.2690000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>47300</v>
       </c>
@@ -946,7 +975,7 @@
         <v>3.472</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>47331</v>
       </c>
@@ -957,7 +986,7 @@
         <v>3.5350000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>47362</v>
       </c>
@@ -968,7 +997,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>47392</v>
       </c>
@@ -979,7 +1008,7 @@
         <v>3.5760000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47423</v>
       </c>
@@ -990,7 +1019,7 @@
         <v>3.7269999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47453</v>
       </c>
@@ -1001,7 +1030,7 @@
         <v>4.2869999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47484</v>
       </c>
@@ -1012,7 +1041,7 @@
         <v>4.7480000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>47515</v>
       </c>
@@ -1023,7 +1052,7 @@
         <v>4.3239999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>47543</v>
       </c>
@@ -1034,7 +1063,7 @@
         <v>3.4790000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>47574</v>
       </c>
@@ -1045,7 +1074,7 @@
         <v>3.1019999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>47604</v>
       </c>
@@ -1056,7 +1085,7 @@
         <v>3.0579999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>47635</v>
       </c>
@@ -1067,7 +1096,7 @@
         <v>3.173</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>47665</v>
       </c>
@@ -1078,7 +1107,7 @@
         <v>3.407</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>47696</v>
       </c>
@@ -1089,7 +1118,7 @@
         <v>3.4510000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>47727</v>
       </c>
@@ -1100,7 +1129,7 @@
         <v>3.4209999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>47757</v>
       </c>
@@ -1111,7 +1140,7 @@
         <v>3.4969999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>47788</v>
       </c>
@@ -1122,7 +1151,7 @@
         <v>3.6549999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>47818</v>
       </c>
@@ -1133,7 +1162,7 @@
         <v>4.2039999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>47849</v>
       </c>
@@ -1144,7 +1173,7 @@
         <v>4.625</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>47880</v>
       </c>
@@ -1155,7 +1184,7 @@
         <v>4.2160000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>47908</v>
       </c>
@@ -1166,7 +1195,7 @@
         <v>3.4260000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>47939</v>
       </c>
@@ -1177,7 +1206,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>47969</v>
       </c>
@@ -1188,7 +1217,7 @@
         <v>3.0139999999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>48000</v>
       </c>
@@ -1199,7 +1228,7 @@
         <v>3.1360000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>48030</v>
       </c>
@@ -1210,7 +1239,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>48061</v>
       </c>
@@ -1221,7 +1250,7 @@
         <v>3.4180000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>48092</v>
       </c>
@@ -1232,7 +1261,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>48122</v>
       </c>
@@ -1243,7 +1272,7 @@
         <v>3.4860000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>48153</v>
       </c>
@@ -1254,7 +1283,7 @@
         <v>3.7149999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>48183</v>
       </c>
@@ -1265,7 +1294,7 @@
         <v>4.3179999999999996</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>48214</v>
       </c>
@@ -1276,7 +1305,7 @@
         <v>4.6550000000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>48245</v>
       </c>
@@ -1287,7 +1316,7 @@
         <v>4.2469999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>48274</v>
       </c>
@@ -1298,7 +1327,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>48305</v>
       </c>
@@ -1309,7 +1338,7 @@
         <v>2.968</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>48335</v>
       </c>
@@ -1320,7 +1349,7 @@
         <v>2.9359999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>48366</v>
       </c>
@@ -1331,7 +1360,7 @@
         <v>3.0510000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>48396</v>
       </c>
@@ -1342,7 +1371,7 @@
         <v>3.2320000000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>48427</v>
       </c>
@@ -1353,7 +1382,7 @@
         <v>3.2839999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>48458</v>
       </c>
@@ -1364,7 +1393,7 @@
         <v>3.2589999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>48488</v>
       </c>
@@ -1375,7 +1404,7 @@
         <v>3.3239999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>48519</v>
       </c>
@@ -1386,7 +1415,7 @@
         <v>3.5390000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>48549</v>
       </c>
@@ -1405,13 +1434,1267 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181BEF81-CE8F-4D5A-B9EC-49C0C8B5AE38}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B2">
+        <v>63.533999999999999</v>
+      </c>
+      <c r="C2">
+        <v>2.9498000000000002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B3">
+        <v>60.07</v>
+      </c>
+      <c r="C3">
+        <v>3.1211000000000002</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B4">
+        <v>59.478999999999999</v>
+      </c>
+      <c r="C4">
+        <v>3.7837999999999998</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B5">
+        <v>57.866</v>
+      </c>
+      <c r="C5">
+        <v>4.1501999999999999</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B6">
+        <v>60.26</v>
+      </c>
+      <c r="C6">
+        <v>7.7126000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B7">
+        <v>64.522999999999996</v>
+      </c>
+      <c r="C7">
+        <v>3.8382000000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B8">
+        <v>90.997</v>
+      </c>
+      <c r="C8">
+        <v>3.0581999999999998</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B9">
+        <v>98.06</v>
+      </c>
+      <c r="C9">
+        <v>2.7736999999999998</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B10">
+        <v>98.513999999999996</v>
+      </c>
+      <c r="C10">
+        <v>2.8881999999999999</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B11">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="C11">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B12">
+        <v>79.22</v>
+      </c>
+      <c r="C12">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B13">
+        <v>82.451999999999998</v>
+      </c>
+      <c r="C13">
+        <v>2.9213499999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B14">
+        <v>89.513999999999996</v>
+      </c>
+      <c r="C14">
+        <v>2.9213499999999999</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B15">
+        <v>86.739000000000004</v>
+      </c>
+      <c r="C15">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>46327</v>
+      </c>
+      <c r="B16">
+        <v>84.328000000000003</v>
+      </c>
+      <c r="C16">
+        <v>3.0339999999999998</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46357</v>
+      </c>
+      <c r="B17">
+        <v>81.686999999999998</v>
+      </c>
+      <c r="C17">
+        <v>3.4929999999999999</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46388</v>
+      </c>
+      <c r="B18">
+        <v>79.489000000000004</v>
+      </c>
+      <c r="C18">
+        <v>3.9159999999999999</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46419</v>
+      </c>
+      <c r="B19">
+        <v>78.034999999999997</v>
+      </c>
+      <c r="C19">
+        <v>3.5739999999999998</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46447</v>
+      </c>
+      <c r="B20">
+        <v>76.573999999999998</v>
+      </c>
+      <c r="C20">
+        <v>2.9009999999999998</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46478</v>
+      </c>
+      <c r="B21">
+        <v>75.399000000000001</v>
+      </c>
+      <c r="C21">
+        <v>2.77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46508</v>
+      </c>
+      <c r="B22">
+        <v>74.591999999999999</v>
+      </c>
+      <c r="C22">
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>46539</v>
+      </c>
+      <c r="B23">
+        <v>73.869</v>
+      </c>
+      <c r="C23">
+        <v>2.9289999999999998</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>46569</v>
+      </c>
+      <c r="B24">
+        <v>73.180000000000007</v>
+      </c>
+      <c r="C24">
+        <v>3.141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>46600</v>
+      </c>
+      <c r="B25">
+        <v>72.683999999999997</v>
+      </c>
+      <c r="C25">
+        <v>3.2149999999999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46631</v>
+      </c>
+      <c r="B26">
+        <v>72.212999999999994</v>
+      </c>
+      <c r="C26">
+        <v>3.2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46661</v>
+      </c>
+      <c r="B27">
+        <v>71.816999999999993</v>
+      </c>
+      <c r="C27">
+        <v>3.2829999999999999</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46692</v>
+      </c>
+      <c r="B28">
+        <v>71.460999999999999</v>
+      </c>
+      <c r="C28">
+        <v>3.5449999999999999</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>46722</v>
+      </c>
+      <c r="B29">
+        <v>71.058999999999997</v>
+      </c>
+      <c r="C29">
+        <v>4.1660000000000004</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>46753</v>
+      </c>
+      <c r="B30">
+        <v>70.715000000000003</v>
+      </c>
+      <c r="C30">
+        <v>4.6109999999999998</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46784</v>
+      </c>
+      <c r="B31">
+        <v>70.424999999999997</v>
+      </c>
+      <c r="C31">
+        <v>4.1829999999999998</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>46813</v>
+      </c>
+      <c r="B32">
+        <v>70.113</v>
+      </c>
+      <c r="C32">
+        <v>3.4220000000000002</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>46844</v>
+      </c>
+      <c r="B33">
+        <v>69.876999999999995</v>
+      </c>
+      <c r="C33">
+        <v>3.1709999999999998</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>46874</v>
+      </c>
+      <c r="B34">
+        <v>69.652000000000001</v>
+      </c>
+      <c r="C34">
+        <v>3.16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>46905</v>
+      </c>
+      <c r="B35">
+        <v>69.375</v>
+      </c>
+      <c r="C35">
+        <v>3.3119999999999998</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46935</v>
+      </c>
+      <c r="B36">
+        <v>69.14</v>
+      </c>
+      <c r="C36">
+        <v>3.5139999999999998</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>46966</v>
+      </c>
+      <c r="B37">
+        <v>68.926000000000002</v>
+      </c>
+      <c r="C37">
+        <v>3.5760000000000001</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>46997</v>
+      </c>
+      <c r="B38">
+        <v>68.716999999999999</v>
+      </c>
+      <c r="C38">
+        <v>3.55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>47027</v>
+      </c>
+      <c r="B39">
+        <v>68.543000000000006</v>
+      </c>
+      <c r="C39">
+        <v>3.601</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>47058</v>
+      </c>
+      <c r="B40">
+        <v>68.346999999999994</v>
+      </c>
+      <c r="C40">
+        <v>3.7519999999999998</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>47088</v>
+      </c>
+      <c r="B41">
+        <v>68.123000000000005</v>
+      </c>
+      <c r="C41">
+        <v>4.3170000000000002</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>47119</v>
+      </c>
+      <c r="B42">
+        <v>67.917000000000002</v>
+      </c>
+      <c r="C42">
+        <v>4.7640000000000002</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>47150</v>
+      </c>
+      <c r="B43">
+        <v>67.733000000000004</v>
+      </c>
+      <c r="C43">
+        <v>4.33</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>47178</v>
+      </c>
+      <c r="B44">
+        <v>67.552999999999997</v>
+      </c>
+      <c r="C44">
+        <v>3.4470000000000001</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>47209</v>
+      </c>
+      <c r="B45">
+        <v>67.394000000000005</v>
+      </c>
+      <c r="C45">
+        <v>3.1619999999999999</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>47239</v>
+      </c>
+      <c r="B46">
+        <v>67.224999999999994</v>
+      </c>
+      <c r="C46">
+        <v>3.1440000000000001</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>47270</v>
+      </c>
+      <c r="B47">
+        <v>67.013999999999996</v>
+      </c>
+      <c r="C47">
+        <v>3.2690000000000001</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47300</v>
+      </c>
+      <c r="B48">
+        <v>66.83</v>
+      </c>
+      <c r="C48">
+        <v>3.472</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47331</v>
+      </c>
+      <c r="B49">
+        <v>66.653999999999996</v>
+      </c>
+      <c r="C49">
+        <v>3.5350000000000001</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>47362</v>
+      </c>
+      <c r="B50">
+        <v>66.503</v>
+      </c>
+      <c r="C50">
+        <v>3.52</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47392</v>
+      </c>
+      <c r="B51">
+        <v>66.353999999999999</v>
+      </c>
+      <c r="C51">
+        <v>3.5760000000000001</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>47423</v>
+      </c>
+      <c r="B52">
+        <v>66.174000000000007</v>
+      </c>
+      <c r="C52">
+        <v>3.7269999999999999</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>47453</v>
+      </c>
+      <c r="B53">
+        <v>65.977000000000004</v>
+      </c>
+      <c r="C53">
+        <v>4.2869999999999999</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>47484</v>
+      </c>
+      <c r="B54">
+        <v>65.787000000000006</v>
+      </c>
+      <c r="C54">
+        <v>4.7480000000000002</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>47515</v>
+      </c>
+      <c r="B55">
+        <v>65.635999999999996</v>
+      </c>
+      <c r="C55">
+        <v>4.3239999999999998</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>47543</v>
+      </c>
+      <c r="B56">
+        <v>65.492999999999995</v>
+      </c>
+      <c r="C56">
+        <v>3.4790000000000001</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>47574</v>
+      </c>
+      <c r="B57">
+        <v>65.349000000000004</v>
+      </c>
+      <c r="C57">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>47604</v>
+      </c>
+      <c r="B58">
+        <v>65.156000000000006</v>
+      </c>
+      <c r="C58">
+        <v>3.0579999999999998</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>47635</v>
+      </c>
+      <c r="B59">
+        <v>64.968999999999994</v>
+      </c>
+      <c r="C59">
+        <v>3.173</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>47665</v>
+      </c>
+      <c r="B60">
+        <v>64.808999999999997</v>
+      </c>
+      <c r="C60">
+        <v>3.407</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>47696</v>
+      </c>
+      <c r="B61">
+        <v>64.644999999999996</v>
+      </c>
+      <c r="C61">
+        <v>3.4510000000000001</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1710,42 +2993,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1770,12 +3032,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>